--- a/downloads/勞動基金月度揭露_可持續更新.xlsx
+++ b/downloads/勞動基金月度揭露_可持續更新.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1670" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1712" uniqueCount="193">
   <si>
     <t>勞動基金運用局｜四大基金月度儀表板</t>
   </si>
@@ -22,7 +22,7 @@
     <t>資料期間</t>
   </si>
   <si>
-    <t>202607</t>
+    <t>202608</t>
   </si>
   <si>
     <t>基金</t>
@@ -277,261 +277,312 @@
     <t>國內106年第一次委託經營(續約)</t>
   </si>
   <si>
+    <t>國內111年第一次委託經營</t>
+  </si>
+  <si>
+    <t>103年委託經營(續約4)</t>
+  </si>
+  <si>
+    <t>104年委託經營(續約4)</t>
+  </si>
+  <si>
+    <t>106年第一次委託經營(續約)</t>
+  </si>
+  <si>
     <t>國內109年第二次委託經營</t>
   </si>
   <si>
-    <t>國內111年第一次委託經營</t>
-  </si>
-  <si>
-    <t>103年委託經營(續約4)</t>
-  </si>
-  <si>
-    <t>104年委託經營(續約4)</t>
-  </si>
-  <si>
-    <t>106年第一次委託經營(續約)</t>
+    <t>解約</t>
+  </si>
+  <si>
+    <t>97-1全球債券型（續約4）</t>
+  </si>
+  <si>
+    <t>聯博</t>
   </si>
   <si>
     <t>新增</t>
   </si>
   <si>
-    <t>解約</t>
+    <t>美元</t>
+  </si>
+  <si>
+    <t>坦伯頓</t>
+  </si>
+  <si>
+    <t>97-2全球增值債券型（續約3）</t>
+  </si>
+  <si>
+    <t>PIMCO</t>
+  </si>
+  <si>
+    <t>97-2全球增值股票型（續約3）</t>
+  </si>
+  <si>
+    <t>JPMorgan（國外）</t>
+  </si>
+  <si>
+    <t>98-1亞太（日本除外）股票型（續約3）</t>
+  </si>
+  <si>
+    <t>景順</t>
+  </si>
+  <si>
+    <t>98-1全球被動股票型（續約3）</t>
+  </si>
+  <si>
+    <t>道富</t>
+  </si>
+  <si>
+    <t>100-1全球基本面指數股票型（續約3）</t>
+  </si>
+  <si>
+    <t>100-1全球不動產有價證券型（續約2）</t>
+  </si>
+  <si>
+    <t>Cohen &amp;Steers</t>
+  </si>
+  <si>
+    <t>101-1全球新興市場債券型（續約2）</t>
+  </si>
+  <si>
+    <t>Pictet</t>
+  </si>
+  <si>
+    <t>101-1全球低波動指數股票型（續約2）</t>
+  </si>
+  <si>
+    <t>102-1全球高股利增值股票型（續約2）</t>
+  </si>
+  <si>
+    <t>瑞萬通博</t>
+  </si>
+  <si>
+    <t>MFS</t>
+  </si>
+  <si>
+    <t>威靈頓</t>
+  </si>
+  <si>
+    <t>102-1全球信用債券型（續約2）</t>
+  </si>
+  <si>
+    <t>RBC</t>
+  </si>
+  <si>
+    <t>盧米斯</t>
+  </si>
+  <si>
+    <t>104-1全球高品質被動股票型（續約2）</t>
+  </si>
+  <si>
+    <t>北美信託</t>
+  </si>
+  <si>
+    <t>L&amp;G</t>
+  </si>
+  <si>
+    <t>Geode</t>
+  </si>
+  <si>
+    <t>104-2全球基礎建設有價證券型（續約2）</t>
+  </si>
+  <si>
+    <t>Magellan</t>
+  </si>
+  <si>
+    <t>RREEF</t>
+  </si>
+  <si>
+    <t>105-1亞太混合指數增值股票型(續約2)</t>
+  </si>
+  <si>
+    <t>106-1全球ESG混合指數被動股票型(續約)</t>
+  </si>
+  <si>
+    <t>DWS</t>
+  </si>
+  <si>
+    <t>106-1絕對報酬債券型(續約)</t>
+  </si>
+  <si>
+    <t>American Century</t>
+  </si>
+  <si>
+    <t>富達</t>
+  </si>
+  <si>
+    <t>TCW</t>
+  </si>
+  <si>
+    <t>107-1絕對報酬股票型（續約）</t>
+  </si>
+  <si>
+    <t>CPR</t>
+  </si>
+  <si>
+    <t>Nomura</t>
+  </si>
+  <si>
+    <t>荷寶</t>
+  </si>
+  <si>
+    <t>109-1全球美元公司增值債券型(續約)</t>
+  </si>
+  <si>
+    <t>Insight</t>
+  </si>
+  <si>
+    <t>110-1全球基礎建設有價證券型</t>
+  </si>
+  <si>
+    <t>CBRE</t>
+  </si>
+  <si>
+    <t>ClearBridge</t>
+  </si>
+  <si>
+    <t>110-1全球多元資產型</t>
+  </si>
+  <si>
+    <t>Ninety One</t>
+  </si>
+  <si>
+    <t>Schroders</t>
+  </si>
+  <si>
+    <t>T. Rowe Price</t>
+  </si>
+  <si>
+    <t>111-1全球氣候變遷增值股票型</t>
+  </si>
+  <si>
+    <t>摩根士丹利</t>
+  </si>
+  <si>
+    <t>111-2絕對報酬債券型</t>
+  </si>
+  <si>
+    <t>PGIM</t>
+  </si>
+  <si>
+    <t>112-1全球被動股票型</t>
+  </si>
+  <si>
+    <t>Amundi</t>
+  </si>
+  <si>
+    <t>113-1全球永續不動產有價證券型</t>
+  </si>
+  <si>
+    <t>Center Square</t>
+  </si>
+  <si>
+    <t>114-1全球氣候轉型被動股票型</t>
+  </si>
+  <si>
+    <t>HSBC</t>
+  </si>
+  <si>
+    <t>UBS</t>
+  </si>
+  <si>
+    <t>96國際平衡型(續約4)</t>
+  </si>
+  <si>
+    <t>97-1全球增值債券型(續約3)</t>
+  </si>
+  <si>
+    <t>97-1全球增值股票型(續約3)</t>
+  </si>
+  <si>
+    <t>98-1亞太(日本除外)主動股票型(續約3)</t>
+  </si>
+  <si>
+    <t>100-1全球基本面指數股票型(續約3)</t>
+  </si>
+  <si>
+    <t>101-1全球低波動指數股票型(續約2)</t>
+  </si>
+  <si>
+    <t>102-1年全球高股利增值股票型(續約2)</t>
+  </si>
+  <si>
+    <t>102-2全球基礎建設有價證券型(續約2)</t>
+  </si>
+  <si>
+    <t>Lazard</t>
+  </si>
+  <si>
+    <t>102-2全球不動產有價證券型(續約2)</t>
+  </si>
+  <si>
+    <t>信安</t>
+  </si>
+  <si>
+    <t>105-1全球多元資產型(續約2)</t>
+  </si>
+  <si>
+    <t>Allianz</t>
+  </si>
+  <si>
+    <t>107-1絕對報酬股票型(續約)</t>
+  </si>
+  <si>
+    <t>100年全球股票型(續約2)</t>
+  </si>
+  <si>
+    <t>101年全球新興市場債券型(續約2)</t>
+  </si>
+  <si>
+    <t>104年全球債券型(續約3)</t>
+  </si>
+  <si>
+    <t>104-1全球高品質被動股票型(續約2)</t>
+  </si>
+  <si>
+    <t>104-2全球基礎建設有價證券型(續約2)</t>
+  </si>
+  <si>
+    <t>104-2全球不動產有價證券型(續約2)</t>
+  </si>
+  <si>
+    <t>104-1全球主權信用增值債券型(續約2)</t>
   </si>
   <si>
     <t>97-1全球主動債券型（續約3）</t>
   </si>
   <si>
-    <t>聯博</t>
-  </si>
-  <si>
-    <t>美元</t>
-  </si>
-  <si>
     <t>富蘭克林坦伯頓</t>
   </si>
   <si>
-    <t>97-2全球增值債券型（續約3）</t>
-  </si>
-  <si>
-    <t>PIMCO</t>
-  </si>
-  <si>
-    <t>97-2全球增值股票型（續約3）</t>
-  </si>
-  <si>
-    <t>JPMorgan（國外）</t>
-  </si>
-  <si>
     <t>98-1亞太（日本除外）主動股票型（續約3）</t>
   </si>
   <si>
-    <t>景順</t>
-  </si>
-  <si>
-    <t>98-1全球被動股票型（續約3）</t>
-  </si>
-  <si>
-    <t>道富</t>
-  </si>
-  <si>
     <t>100-1全球基本面指數被動股票型（續約3）</t>
   </si>
   <si>
-    <t>100-1全球不動產有價證券型（續約2）</t>
-  </si>
-  <si>
-    <t>Cohen &amp;Steers</t>
-  </si>
-  <si>
     <t>101-1全球新興市場主動債券型（續約2）</t>
   </si>
   <si>
-    <t>Pictet</t>
-  </si>
-  <si>
     <t>101-1全球低波動指數被動股票型（續約2）</t>
   </si>
   <si>
-    <t>102-1全球高股利增值股票型（續約2）</t>
-  </si>
-  <si>
-    <t>瑞萬通博</t>
-  </si>
-  <si>
-    <t>MFS</t>
-  </si>
-  <si>
-    <t>威靈頓</t>
-  </si>
-  <si>
     <t>102-1全球信用主動債券型（續約2）</t>
   </si>
   <si>
-    <t>RBC</t>
-  </si>
-  <si>
-    <t>盧米斯</t>
-  </si>
-  <si>
-    <t>104-1全球高品質被動股票型（續約2）</t>
-  </si>
-  <si>
-    <t>北美信託</t>
-  </si>
-  <si>
-    <t>L&amp;G</t>
-  </si>
-  <si>
-    <t>Geode</t>
-  </si>
-  <si>
-    <t>104-2全球基礎建設有價證券型（續約2）</t>
-  </si>
-  <si>
-    <t>Magellan</t>
-  </si>
-  <si>
-    <t>RREEF</t>
-  </si>
-  <si>
     <t>105-1亞太混合指數增值股票型(續約)</t>
   </si>
   <si>
-    <t>106-1全球ESG混合指數被動股票型(續約)</t>
-  </si>
-  <si>
-    <t>DWS</t>
-  </si>
-  <si>
-    <t>106-1絕對報酬債券型(續約)</t>
-  </si>
-  <si>
-    <t>American Century</t>
-  </si>
-  <si>
-    <t>富達</t>
-  </si>
-  <si>
-    <t>TCW</t>
-  </si>
-  <si>
-    <t>107-1絕對報酬股票型（續約）</t>
-  </si>
-  <si>
-    <t>CPR</t>
-  </si>
-  <si>
-    <t>Nomura</t>
-  </si>
-  <si>
-    <t>荷寶</t>
-  </si>
-  <si>
-    <t>109-1全球美元公司增值債券型(續約)</t>
-  </si>
-  <si>
-    <t>Insight</t>
-  </si>
-  <si>
-    <t>110-1全球基礎建設有價證券型</t>
-  </si>
-  <si>
-    <t>CBRE</t>
-  </si>
-  <si>
-    <t>ClearBridge</t>
-  </si>
-  <si>
-    <t>110-1全球多元資產型</t>
-  </si>
-  <si>
-    <t>Ninety One</t>
-  </si>
-  <si>
-    <t>Schroders</t>
-  </si>
-  <si>
-    <t>T. Rowe Price</t>
-  </si>
-  <si>
-    <t>111-1全球氣候變遷增值股票型</t>
-  </si>
-  <si>
     <t>LGIM</t>
   </si>
   <si>
-    <t>摩根士丹利</t>
-  </si>
-  <si>
-    <t>111-2絕對報酬債券型</t>
-  </si>
-  <si>
-    <t>PGIM</t>
-  </si>
-  <si>
-    <t>112-1全球被動股票型</t>
-  </si>
-  <si>
-    <t>Amundi</t>
-  </si>
-  <si>
-    <t>113-1全球永續不動產有價證券型</t>
-  </si>
-  <si>
-    <t>Center Square</t>
-  </si>
-  <si>
-    <t>114-1全球氣候轉型被動股票型</t>
-  </si>
-  <si>
-    <t>HSBC</t>
-  </si>
-  <si>
-    <t>UBS</t>
-  </si>
-  <si>
-    <t>96國際平衡型(續約4)</t>
-  </si>
-  <si>
-    <t>97-1全球增值債券型(續約3)</t>
-  </si>
-  <si>
-    <t>97-1全球增值股票型(續約3)</t>
-  </si>
-  <si>
-    <t>98-1亞太(日本除外)主動股票型(續約3)</t>
-  </si>
-  <si>
     <t>100-1全球基本面指數被動股票型(續約3)</t>
   </si>
   <si>
     <t>101-1全球低波動指數被動股票型(續約2)</t>
   </si>
   <si>
-    <t>102-1年全球高股利增值股票型(續約2)</t>
-  </si>
-  <si>
-    <t>102-2全球基礎建設有價證券型(續約2)</t>
-  </si>
-  <si>
-    <t>Lazard</t>
-  </si>
-  <si>
-    <t>102-2全球不動產有價證券型(續約2)</t>
-  </si>
-  <si>
-    <t>信安</t>
-  </si>
-  <si>
-    <t>105-1全球多元資產型(續約2)</t>
-  </si>
-  <si>
-    <t>Allianz</t>
-  </si>
-  <si>
-    <t>107-1絕對報酬股票型(續約)</t>
-  </si>
-  <si>
     <t>100年全球主動股票型(續約2)</t>
   </si>
   <si>
@@ -541,34 +592,7 @@
     <t>104年全球主動債券型(續約3)</t>
   </si>
   <si>
-    <t>104-1全球高品質被動股票型(續約2)</t>
-  </si>
-  <si>
-    <t>104-2全球基礎建設有價證券型(續約2)</t>
-  </si>
-  <si>
-    <t>104-2全球不動產有價證券型(續約2)</t>
-  </si>
-  <si>
     <t>111-1全球氣候變遷股票型</t>
-  </si>
-  <si>
-    <t>100-1全球基本面指數被動股票型（續約2）</t>
-  </si>
-  <si>
-    <t>104-2全球基礎建設有價證券型（續約）</t>
-  </si>
-  <si>
-    <t>105-1全球多元資產型(續約)</t>
-  </si>
-  <si>
-    <t>柏瑞</t>
-  </si>
-  <si>
-    <t>100-1全球基本面指數被動股票型(續約2)</t>
-  </si>
-  <si>
-    <t>104-1全球主權信用增值債券型(續約2)</t>
   </si>
 </sst>
 </file>
@@ -1009,7 +1033,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="1">
-        <v>5971891365843</v>
+        <v>5978543425091</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1017,7 +1041,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="1">
-        <v>1201392132968</v>
+        <v>1203065126674</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -1025,7 +1049,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="1">
-        <v>1656620647003</v>
+        <v>1674409178658</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1033,7 +1057,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="1">
-        <v>886247346634</v>
+        <v>905688678364</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1055,7 +1079,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D74"/>
+  <dimension ref="A1:D85"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="22" customWidth="1"/>
@@ -1085,10 +1109,10 @@
         <v>13</v>
       </c>
       <c r="C2" s="1">
-        <v>2045726190154</v>
+        <v>2063615764168</v>
       </c>
       <c r="D2" s="5">
-        <v>0.34259999999999996</v>
+        <v>0.3452</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1099,10 +1123,10 @@
         <v>14</v>
       </c>
       <c r="C3" s="1">
-        <v>478291754572</v>
+        <v>484632062355</v>
       </c>
       <c r="D3" s="5">
-        <v>0.0801</v>
+        <v>0.08109999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1113,10 +1137,10 @@
         <v>15</v>
       </c>
       <c r="C4" s="1">
-        <v>152803509826</v>
+        <v>154840949506</v>
       </c>
       <c r="D4" s="5">
-        <v>0.0256</v>
+        <v>0.0259</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1127,10 +1151,10 @@
         <v>16</v>
       </c>
       <c r="C5" s="1">
-        <v>251734539206</v>
+        <v>254658621638</v>
       </c>
       <c r="D5" s="5">
-        <v>0.0421</v>
+        <v>0.0426</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1141,10 +1165,10 @@
         <v>17</v>
       </c>
       <c r="C6" s="1">
-        <v>311555741999</v>
+        <v>316654621891</v>
       </c>
       <c r="D6" s="5">
-        <v>0.052199999999999996</v>
+        <v>0.053</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1155,7 +1179,7 @@
         <v>18</v>
       </c>
       <c r="C7" s="1">
-        <v>851340644551</v>
+        <v>852829508778</v>
       </c>
       <c r="D7" s="5">
         <v>0.1426</v>
@@ -1169,10 +1193,10 @@
         <v>19</v>
       </c>
       <c r="C8" s="1">
-        <v>721154157630</v>
+        <v>724461087908</v>
       </c>
       <c r="D8" s="5">
-        <v>0.1208</v>
+        <v>0.12119999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1183,10 +1207,10 @@
         <v>20</v>
       </c>
       <c r="C9" s="1">
-        <v>84027862506</v>
+        <v>82763581167</v>
       </c>
       <c r="D9" s="5">
-        <v>0.0141</v>
+        <v>0.0138</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1197,10 +1221,10 @@
         <v>21</v>
       </c>
       <c r="C10" s="1">
-        <v>46158624415</v>
+        <v>45604839703</v>
       </c>
       <c r="D10" s="5">
-        <v>0.0077</v>
+        <v>0.0076</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1211,10 +1235,10 @@
         <v>22</v>
       </c>
       <c r="C11" s="1">
-        <v>3926165175689</v>
+        <v>3914927660923</v>
       </c>
       <c r="D11" s="5">
-        <v>0.6574</v>
+        <v>0.6548</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1225,10 +1249,10 @@
         <v>23</v>
       </c>
       <c r="C12" s="1">
-        <v>1171597084307</v>
+        <v>1197514153024</v>
       </c>
       <c r="D12" s="5">
-        <v>0.1962</v>
+        <v>0.2003</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1239,10 +1263,10 @@
         <v>24</v>
       </c>
       <c r="C13" s="1">
-        <v>2754568091382</v>
+        <v>2717413507899</v>
       </c>
       <c r="D13" s="5">
-        <v>0.4612</v>
+        <v>0.4545</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1253,10 +1277,10 @@
         <v>25</v>
       </c>
       <c r="C14" s="1">
-        <v>596266506088</v>
+        <v>591163249008</v>
       </c>
       <c r="D14" s="5">
-        <v>0.0998</v>
+        <v>0.0989</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1267,10 +1291,10 @@
         <v>26</v>
       </c>
       <c r="C15" s="1">
-        <v>1574426402328</v>
+        <v>1563192121075</v>
       </c>
       <c r="D15" s="5">
-        <v>0.2636</v>
+        <v>0.2614</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1281,10 +1305,10 @@
         <v>27</v>
       </c>
       <c r="C16" s="1">
-        <v>583875182966</v>
+        <v>563058137816</v>
       </c>
       <c r="D16" s="5">
-        <v>0.0978</v>
+        <v>0.0942</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1295,7 +1319,7 @@
         <v>28</v>
       </c>
       <c r="C17" s="1">
-        <v>5971891365843</v>
+        <v>5978543425091</v>
       </c>
       <c r="D17" s="5">
         <v>1</v>
@@ -1309,10 +1333,10 @@
         <v>13</v>
       </c>
       <c r="C18" s="1">
-        <v>542814149168</v>
+        <v>561545393270</v>
       </c>
       <c r="D18" s="5">
-        <v>0.4518</v>
+        <v>0.4668</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1323,10 +1347,10 @@
         <v>14</v>
       </c>
       <c r="C19" s="1">
-        <v>243818801079</v>
+        <v>273630108744</v>
       </c>
       <c r="D19" s="5">
-        <v>0.2029</v>
+        <v>0.2274</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1337,10 +1361,10 @@
         <v>15</v>
       </c>
       <c r="C20" s="1">
-        <v>73524579727</v>
+        <v>75730003405</v>
       </c>
       <c r="D20" s="5">
-        <v>0.061200000000000004</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1351,10 +1375,10 @@
         <v>16</v>
       </c>
       <c r="C21" s="1">
-        <v>86936556465</v>
+        <v>84270515805</v>
       </c>
       <c r="D21" s="5">
-        <v>0.0724</v>
+        <v>0.07</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1365,10 +1389,10 @@
         <v>17</v>
       </c>
       <c r="C22" s="1">
-        <v>86679774630</v>
+        <v>80897733770</v>
       </c>
       <c r="D22" s="5">
-        <v>0.0721</v>
+        <v>0.0673</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1379,10 +1403,10 @@
         <v>18</v>
       </c>
       <c r="C23" s="1">
-        <v>51854437267</v>
+        <v>47017031546</v>
       </c>
       <c r="D23" s="5">
-        <v>0.0432</v>
+        <v>0.0391</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1393,10 +1417,10 @@
         <v>19</v>
       </c>
       <c r="C24" s="1">
-        <v>29814460239</v>
+        <v>25870844377</v>
       </c>
       <c r="D24" s="5">
-        <v>0.0248</v>
+        <v>0.0215</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1407,10 +1431,10 @@
         <v>20</v>
       </c>
       <c r="C25" s="1">
-        <v>22039977028</v>
+        <v>21146187169</v>
       </c>
       <c r="D25" s="5">
-        <v>0.0184</v>
+        <v>0.0176</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1435,10 +1459,10 @@
         <v>22</v>
       </c>
       <c r="C27" s="1">
-        <v>658577983800</v>
+        <v>641519733404</v>
       </c>
       <c r="D27" s="5">
-        <v>0.5482</v>
+        <v>0.5332</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1449,10 +1473,10 @@
         <v>23</v>
       </c>
       <c r="C28" s="1">
-        <v>183853928809</v>
+        <v>179152414930</v>
       </c>
       <c r="D28" s="5">
-        <v>0.153</v>
+        <v>0.1489</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1463,10 +1487,10 @@
         <v>24</v>
       </c>
       <c r="C29" s="1">
-        <v>474724054991</v>
+        <v>462367318474</v>
       </c>
       <c r="D29" s="5">
-        <v>0.39520000000000005</v>
+        <v>0.3843</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1477,10 +1501,10 @@
         <v>25</v>
       </c>
       <c r="C30" s="1">
-        <v>110143623315</v>
+        <v>107811891675</v>
       </c>
       <c r="D30" s="5">
-        <v>0.0917</v>
+        <v>0.08960000000000001</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1491,10 +1515,10 @@
         <v>26</v>
       </c>
       <c r="C31" s="1">
-        <v>243869586211</v>
+        <v>242570109923</v>
       </c>
       <c r="D31" s="5">
-        <v>0.203</v>
+        <v>0.2016</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1505,10 +1529,10 @@
         <v>27</v>
       </c>
       <c r="C32" s="1">
-        <v>120710845465</v>
+        <v>111985316876</v>
       </c>
       <c r="D32" s="5">
-        <v>0.1005</v>
+        <v>0.0931</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1519,7 +1543,7 @@
         <v>28</v>
       </c>
       <c r="C33" s="1">
-        <v>1201392132968</v>
+        <v>1203065126674</v>
       </c>
       <c r="D33" s="5">
         <v>1</v>
@@ -1533,10 +1557,10 @@
         <v>13</v>
       </c>
       <c r="C34" s="1">
-        <v>1130233744952</v>
+        <v>1152019301183</v>
       </c>
       <c r="D34" s="5">
-        <v>0.6822</v>
+        <v>0.6881</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1547,10 +1571,10 @@
         <v>14</v>
       </c>
       <c r="C35" s="1">
-        <v>162858626420</v>
+        <v>164027980784</v>
       </c>
       <c r="D35" s="5">
-        <v>0.0983</v>
+        <v>0.09789999999999999</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1561,10 +1585,10 @@
         <v>15</v>
       </c>
       <c r="C36" s="1">
-        <v>43160086648</v>
+        <v>37793044438</v>
       </c>
       <c r="D36" s="5">
-        <v>0.026099999999999998</v>
+        <v>0.0226</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1575,10 +1599,10 @@
         <v>16</v>
       </c>
       <c r="C37" s="1">
-        <v>72726377661</v>
+        <v>75021076190</v>
       </c>
       <c r="D37" s="5">
-        <v>0.043899999999999995</v>
+        <v>0.044800000000000006</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1589,7 +1613,7 @@
         <v>29</v>
       </c>
       <c r="C38" s="1">
-        <v>1569739937</v>
+        <v>1568394036</v>
       </c>
       <c r="D38" s="5">
         <v>0.0009</v>
@@ -1603,10 +1627,10 @@
         <v>30</v>
       </c>
       <c r="C39" s="1">
-        <v>750000000</v>
+        <v>1330000000</v>
       </c>
       <c r="D39" s="5">
-        <v>0.0005</v>
+        <v>0.0008</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1617,10 +1641,10 @@
         <v>31</v>
       </c>
       <c r="C40" s="1">
-        <v>33959565172</v>
+        <v>32957877154</v>
       </c>
       <c r="D40" s="5">
-        <v>0.020499999999999997</v>
+        <v>0.0197</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1631,10 +1655,10 @@
         <v>17</v>
       </c>
       <c r="C41" s="1">
-        <v>513267409855</v>
+        <v>529578251001</v>
       </c>
       <c r="D41" s="5">
-        <v>0.3098</v>
+        <v>0.31629999999999997</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1645,10 +1669,10 @@
         <v>18</v>
       </c>
       <c r="C42" s="1">
-        <v>301941939259</v>
+        <v>309742677580</v>
       </c>
       <c r="D42" s="5">
-        <v>0.1822</v>
+        <v>0.18510000000000001</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1659,10 +1683,10 @@
         <v>19</v>
       </c>
       <c r="C43" s="1">
-        <v>190717945389</v>
+        <v>197483522493</v>
       </c>
       <c r="D43" s="5">
-        <v>0.1151</v>
+        <v>0.11800000000000001</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -1673,7 +1697,7 @@
         <v>20</v>
       </c>
       <c r="C44" s="1">
-        <v>100125263652</v>
+        <v>101099300977</v>
       </c>
       <c r="D44" s="5">
         <v>0.0604</v>
@@ -1687,7 +1711,7 @@
         <v>21</v>
       </c>
       <c r="C45" s="1">
-        <v>11098730218</v>
+        <v>11159854110</v>
       </c>
       <c r="D45" s="5">
         <v>0.0067</v>
@@ -1701,10 +1725,10 @@
         <v>22</v>
       </c>
       <c r="C46" s="1">
-        <v>526386902051</v>
+        <v>522389877475</v>
       </c>
       <c r="D46" s="5">
-        <v>0.3178</v>
+        <v>0.3119</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -1715,10 +1739,10 @@
         <v>23</v>
       </c>
       <c r="C47" s="1">
-        <v>68461127545</v>
+        <v>76846540738</v>
       </c>
       <c r="D47" s="5">
-        <v>0.041299999999999996</v>
+        <v>0.045899999999999996</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -1729,10 +1753,10 @@
         <v>24</v>
       </c>
       <c r="C48" s="1">
-        <v>457925774506</v>
+        <v>445543336737</v>
       </c>
       <c r="D48" s="5">
-        <v>0.27649999999999997</v>
+        <v>0.266</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -1743,10 +1767,10 @@
         <v>25</v>
       </c>
       <c r="C49" s="1">
-        <v>94809693597</v>
+        <v>93455160050</v>
       </c>
       <c r="D49" s="5">
-        <v>0.057300000000000004</v>
+        <v>0.0558</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -1757,10 +1781,10 @@
         <v>26</v>
       </c>
       <c r="C50" s="1">
-        <v>224986107597</v>
+        <v>226784629742</v>
       </c>
       <c r="D50" s="5">
-        <v>0.1358</v>
+        <v>0.1354</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -1771,10 +1795,10 @@
         <v>27</v>
       </c>
       <c r="C51" s="1">
-        <v>138129973312</v>
+        <v>125303546945</v>
       </c>
       <c r="D51" s="5">
-        <v>0.0834</v>
+        <v>0.0748</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -1785,7 +1809,7 @@
         <v>28</v>
       </c>
       <c r="C52" s="1">
-        <v>1656620647003</v>
+        <v>1674409178658</v>
       </c>
       <c r="D52" s="5">
         <v>1</v>
@@ -1799,10 +1823,10 @@
         <v>13</v>
       </c>
       <c r="C53" s="1">
-        <v>1130233744952</v>
+        <v>1152019301183</v>
       </c>
       <c r="D53" s="5">
-        <v>0.6822</v>
+        <v>0.6881</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -1813,94 +1837,94 @@
         <v>22</v>
       </c>
       <c r="C54" s="1">
-        <v>1130233744952</v>
+        <v>1152019301183</v>
       </c>
       <c r="D54" s="5">
-        <v>0.6822</v>
+        <v>0.6881</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B55" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C55" s="1">
-        <v>542143193531</v>
+        <v>30</v>
       </c>
       <c r="D55" s="5">
-        <v>0.6117</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B56" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C56" s="1">
-        <v>42496498692</v>
+        <v>88</v>
       </c>
       <c r="D56" s="5">
-        <v>0.048</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B57" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C57" s="1">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="D57" s="5">
-        <v>0</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B58" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C58" s="1">
-        <v>15470496937</v>
+        <v>49</v>
       </c>
       <c r="D58" s="5">
-        <v>0.0174</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B59" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="C59" s="1">
-        <v>61212952203</v>
+        <v>29</v>
       </c>
       <c r="D59" s="5">
-        <v>0.0691</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B60" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C60" s="1">
-        <v>232196292425</v>
+        <v>9</v>
       </c>
       <c r="D60" s="5">
-        <v>0.262</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -1908,13 +1932,13 @@
         <v>8</v>
       </c>
       <c r="B61" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C61" s="1">
-        <v>190766953274</v>
+        <v>553576143135</v>
       </c>
       <c r="D61" s="5">
-        <v>0.2152</v>
+        <v>0.6112</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -1922,13 +1946,13 @@
         <v>8</v>
       </c>
       <c r="B62" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C62" s="1">
-        <v>108506446162</v>
+        <v>42428446974</v>
       </c>
       <c r="D62" s="5">
-        <v>0.12240000000000001</v>
+        <v>0.046799999999999994</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -1936,13 +1960,13 @@
         <v>8</v>
       </c>
       <c r="B63" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C63" s="1">
-        <v>59219852253</v>
+        <v>0</v>
       </c>
       <c r="D63" s="5">
-        <v>0.0668</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -1950,13 +1974,13 @@
         <v>8</v>
       </c>
       <c r="B64" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C64" s="1">
-        <v>23040654859</v>
+        <v>13721396702</v>
       </c>
       <c r="D64" s="5">
-        <v>0.026000000000000002</v>
+        <v>0.0152</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -1964,13 +1988,13 @@
         <v>8</v>
       </c>
       <c r="B65" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C65" s="1">
-        <v>344104153103</v>
+        <v>63040542871</v>
       </c>
       <c r="D65" s="5">
-        <v>0.3883</v>
+        <v>0.0696</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -1978,13 +2002,13 @@
         <v>8</v>
       </c>
       <c r="B66" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C66" s="1">
-        <v>100575817739</v>
+        <v>240900220373</v>
       </c>
       <c r="D66" s="5">
-        <v>0.11349999999999999</v>
+        <v>0.266</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -1992,13 +2016,13 @@
         <v>8</v>
       </c>
       <c r="B67" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C67" s="1">
-        <v>243528335364</v>
+        <v>193485536215</v>
       </c>
       <c r="D67" s="5">
-        <v>0.2748</v>
+        <v>0.21359999999999998</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -2006,13 +2030,13 @@
         <v>8</v>
       </c>
       <c r="B68" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C68" s="1">
-        <v>43171984301</v>
+        <v>110471920022</v>
       </c>
       <c r="D68" s="5">
-        <v>0.0487</v>
+        <v>0.122</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -2020,13 +2044,13 @@
         <v>8</v>
       </c>
       <c r="B69" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C69" s="1">
-        <v>170076314183</v>
+        <v>59995886430</v>
       </c>
       <c r="D69" s="5">
-        <v>0.19190000000000002</v>
+        <v>0.0662</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -2034,13 +2058,13 @@
         <v>8</v>
       </c>
       <c r="B70" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C70" s="1">
-        <v>30280036880</v>
+        <v>23017729763</v>
       </c>
       <c r="D70" s="5">
-        <v>0.0342</v>
+        <v>0.0254</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -2048,13 +2072,13 @@
         <v>8</v>
       </c>
       <c r="B71" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C71" s="1">
-        <v>886247346634</v>
+        <v>352112535229</v>
       </c>
       <c r="D71" s="5">
-        <v>1</v>
+        <v>0.38880000000000003</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
@@ -2062,13 +2086,13 @@
         <v>8</v>
       </c>
       <c r="B72" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C72" s="1">
-        <v>542143193531</v>
+        <v>108898032465</v>
       </c>
       <c r="D72" s="5">
-        <v>0.6117</v>
+        <v>0.1202</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
@@ -2076,13 +2100,13 @@
         <v>8</v>
       </c>
       <c r="B73" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C73" s="1">
-        <v>344104153103</v>
+        <v>243214502764</v>
       </c>
       <c r="D73" s="5">
-        <v>0.3883</v>
+        <v>0.2686</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
@@ -2090,13 +2114,167 @@
         <v>8</v>
       </c>
       <c r="B74" t="s">
+        <v>25</v>
+      </c>
+      <c r="C74" s="1">
+        <v>42562821561</v>
+      </c>
+      <c r="D74" s="5">
+        <v>0.047</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>8</v>
+      </c>
+      <c r="B75" t="s">
+        <v>26</v>
+      </c>
+      <c r="C75" s="1">
+        <v>171023525266</v>
+      </c>
+      <c r="D75" s="5">
+        <v>0.1889</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>8</v>
+      </c>
+      <c r="B76" t="s">
+        <v>27</v>
+      </c>
+      <c r="C76" s="1">
+        <v>29628155937</v>
+      </c>
+      <c r="D76" s="5">
+        <v>0.0327</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>8</v>
+      </c>
+      <c r="B77" t="s">
+        <v>28</v>
+      </c>
+      <c r="C77" s="1">
+        <v>905688678364</v>
+      </c>
+      <c r="D77" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>8</v>
+      </c>
+      <c r="B78" t="s">
+        <v>13</v>
+      </c>
+      <c r="C78" s="1">
+        <v>553576143135</v>
+      </c>
+      <c r="D78" s="5">
+        <v>0.6112</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>8</v>
+      </c>
+      <c r="B79" t="s">
+        <v>22</v>
+      </c>
+      <c r="C79" s="1">
+        <v>352112535229</v>
+      </c>
+      <c r="D79" s="5">
+        <v>0.38880000000000003</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>8</v>
+      </c>
+      <c r="B80" t="s">
         <v>18</v>
       </c>
-      <c r="C74" s="1">
-        <v>434295288638</v>
-      </c>
-      <c r="D74" s="5">
-        <v>0.49</v>
+      <c r="C80" s="1">
+        <v>436700038979</v>
+      </c>
+      <c r="D80" s="5">
+        <v>0.48219999999999996</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>8</v>
+      </c>
+      <c r="B81" t="s">
+        <v>28</v>
+      </c>
+      <c r="C81" s="1">
+        <v>3</v>
+      </c>
+      <c r="D81" s="5">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>8</v>
+      </c>
+      <c r="B82" t="s">
+        <v>28</v>
+      </c>
+      <c r="C82" s="1">
+        <v>75</v>
+      </c>
+      <c r="D82" s="5">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>8</v>
+      </c>
+      <c r="B83" t="s">
+        <v>28</v>
+      </c>
+      <c r="C83" s="1">
+        <v>8</v>
+      </c>
+      <c r="D83" s="5">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>8</v>
+      </c>
+      <c r="B84" t="s">
+        <v>28</v>
+      </c>
+      <c r="C84" s="1">
+        <v>31</v>
+      </c>
+      <c r="D84" s="5">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>8</v>
+      </c>
+      <c r="B85" t="s">
+        <v>28</v>
+      </c>
+      <c r="C85" s="1">
+        <v>39</v>
+      </c>
+      <c r="D85" s="5">
+        <v>0.02</v>
       </c>
     </row>
   </sheetData>
@@ -2163,10 +2341,10 @@
         <v>53037175831</v>
       </c>
       <c r="E2" s="1">
-        <v>103171495458</v>
+        <v>131295249313</v>
       </c>
       <c r="F2" s="7">
-        <v>-14044944939</v>
+        <v>28123753855</v>
       </c>
       <c r="G2" t="s">
         <v>44</v>
@@ -2176,7 +2354,7 @@
       </c>
       <c r="I2" s="5"/>
       <c r="J2" s="5">
-        <v>0.0527</v>
+        <v>0.057999999999999996</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -2193,10 +2371,10 @@
         <v>6829066771</v>
       </c>
       <c r="E3" s="1">
-        <v>23175252518</v>
+        <v>28945859286</v>
       </c>
       <c r="F3" s="7">
-        <v>-3769084120</v>
+        <v>5770606768</v>
       </c>
       <c r="G3" t="s">
         <v>44</v>
@@ -2206,7 +2384,7 @@
       </c>
       <c r="I3" s="5"/>
       <c r="J3" s="5">
-        <v>0.2113</v>
+        <v>0.2162</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -2223,10 +2401,10 @@
         <v>25455695879</v>
       </c>
       <c r="E4" s="1">
-        <v>58059587887</v>
+        <v>72345554361</v>
       </c>
       <c r="F4" s="7">
-        <v>-8430853510</v>
+        <v>14285966474</v>
       </c>
       <c r="G4" t="s">
         <v>44</v>
@@ -2236,7 +2414,7 @@
       </c>
       <c r="I4" s="5"/>
       <c r="J4" s="5">
-        <v>0.1198</v>
+        <v>0.1246</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -2253,10 +2431,10 @@
         <v>7430070832</v>
       </c>
       <c r="E5" s="1">
-        <v>12830277484</v>
+        <v>14896602228</v>
       </c>
       <c r="F5" s="7">
-        <v>-2570992363</v>
+        <v>2066324744</v>
       </c>
       <c r="G5" t="s">
         <v>44</v>
@@ -2266,7 +2444,7 @@
       </c>
       <c r="I5" s="5"/>
       <c r="J5" s="5">
-        <v>0.1198</v>
+        <v>0.1246</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -2283,10 +2461,10 @@
         <v>10445113310</v>
       </c>
       <c r="E6" s="1">
-        <v>26081939969</v>
+        <v>30272112263</v>
       </c>
       <c r="F6" s="7">
-        <v>-3170801195</v>
+        <v>4190172294</v>
       </c>
       <c r="G6" t="s">
         <v>44</v>
@@ -2296,7 +2474,7 @@
       </c>
       <c r="I6" s="5"/>
       <c r="J6" s="5">
-        <v>0.22089999999999999</v>
+        <v>0.22579999999999997</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -2313,10 +2491,10 @@
         <v>29101525086</v>
       </c>
       <c r="E7" s="1">
-        <v>79596508766</v>
+        <v>89073113838</v>
       </c>
       <c r="F7" s="7">
-        <v>-9961655016</v>
+        <v>9476605072</v>
       </c>
       <c r="G7" t="s">
         <v>44</v>
@@ -2326,7 +2504,7 @@
       </c>
       <c r="I7" s="5"/>
       <c r="J7" s="5">
-        <v>1.6263999999999998</v>
+        <v>1.9274</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -2343,10 +2521,10 @@
         <v>15198354580</v>
       </c>
       <c r="E8" s="1">
-        <v>40396399644</v>
+        <v>52444842279</v>
       </c>
       <c r="F8" s="7">
-        <v>-6265873016</v>
+        <v>12048442635</v>
       </c>
       <c r="G8" t="s">
         <v>44</v>
@@ -2356,7 +2534,7 @@
       </c>
       <c r="I8" s="5"/>
       <c r="J8" s="5">
-        <v>0.1191</v>
+        <v>0.12390000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -2373,10 +2551,10 @@
         <v>20913151881</v>
       </c>
       <c r="E9" s="1">
-        <v>38985680063</v>
+        <v>46315207979</v>
       </c>
       <c r="F9" s="7">
-        <v>-7022091552</v>
+        <v>7329527916</v>
       </c>
       <c r="G9" t="s">
         <v>44</v>
@@ -2386,7 +2564,7 @@
       </c>
       <c r="I9" s="5"/>
       <c r="J9" s="5">
-        <v>0.1191</v>
+        <v>0.12390000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -2403,10 +2581,10 @@
         <v>37517851631</v>
       </c>
       <c r="E10" s="1">
-        <v>56336151382</v>
+        <v>61515786308</v>
       </c>
       <c r="F10" s="7">
-        <v>-4431675502</v>
+        <v>5179634926</v>
       </c>
       <c r="G10" t="s">
         <v>44</v>
@@ -2416,7 +2594,7 @@
       </c>
       <c r="I10" s="5"/>
       <c r="J10" s="5">
-        <v>0.36619999999999997</v>
+        <v>0.4636</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -2433,10 +2611,10 @@
         <v>39053243767</v>
       </c>
       <c r="E11" s="1">
-        <v>55897686273</v>
+        <v>61116322916</v>
       </c>
       <c r="F11" s="7">
-        <v>-4817199812</v>
+        <v>5218636643</v>
       </c>
       <c r="G11" t="s">
         <v>44</v>
@@ -2446,7 +2624,7 @@
       </c>
       <c r="I11" s="5"/>
       <c r="J11" s="5">
-        <v>0.36619999999999997</v>
+        <v>0.4636</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
@@ -2463,10 +2641,10 @@
         <v>15841461125</v>
       </c>
       <c r="E12" s="1">
-        <v>41322318010</v>
+        <v>46531529917</v>
       </c>
       <c r="F12" s="7">
-        <v>-3888439594</v>
+        <v>5209211907</v>
       </c>
       <c r="G12" t="s">
         <v>44</v>
@@ -2476,7 +2654,7 @@
       </c>
       <c r="I12" s="5"/>
       <c r="J12" s="5">
-        <v>0.2302</v>
+        <v>0.235</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
@@ -2493,10 +2671,10 @@
         <v>23658255796</v>
       </c>
       <c r="E13" s="1">
-        <v>40415302192</v>
+        <v>42974248851</v>
       </c>
       <c r="F13" s="7">
-        <v>-132920971</v>
+        <v>2558946659</v>
       </c>
       <c r="G13" t="s">
         <v>44</v>
@@ -2506,7 +2684,7 @@
       </c>
       <c r="I13" s="5"/>
       <c r="J13" s="5">
-        <v>0.6726000000000001</v>
+        <v>0.7592</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -2523,10 +2701,10 @@
         <v>20210724588</v>
       </c>
       <c r="E14" s="1">
-        <v>34144349128</v>
+        <v>35903069239</v>
       </c>
       <c r="F14" s="7">
-        <v>-35804097</v>
+        <v>1758720111</v>
       </c>
       <c r="G14" t="s">
         <v>44</v>
@@ -2536,7 +2714,7 @@
       </c>
       <c r="I14" s="5"/>
       <c r="J14" s="5">
-        <v>0.6726000000000001</v>
+        <v>0.7592</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -2553,10 +2731,10 @@
         <v>19554752074</v>
       </c>
       <c r="E15" s="1">
-        <v>33339520716</v>
+        <v>35279643743</v>
       </c>
       <c r="F15" s="7">
-        <v>-150450416</v>
+        <v>1940123027</v>
       </c>
       <c r="G15" t="s">
         <v>44</v>
@@ -2566,7 +2744,7 @@
       </c>
       <c r="I15" s="5"/>
       <c r="J15" s="5">
-        <v>0.6726000000000001</v>
+        <v>0.7592</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -2583,10 +2761,10 @@
         <v>16812903049</v>
       </c>
       <c r="E16" s="1">
-        <v>28296630865</v>
+        <v>29877197749</v>
       </c>
       <c r="F16" s="7">
-        <v>-194181980</v>
+        <v>1580566884</v>
       </c>
       <c r="G16" t="s">
         <v>44</v>
@@ -2596,7 +2774,7 @@
       </c>
       <c r="I16" s="5"/>
       <c r="J16" s="5">
-        <v>0.6726000000000001</v>
+        <v>0.7592</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
@@ -2613,10 +2791,10 @@
         <v>24098049298</v>
       </c>
       <c r="E17" s="1">
-        <v>41223752467</v>
+        <v>43591301080</v>
       </c>
       <c r="F17" s="7">
-        <v>-219117658</v>
+        <v>2367548613</v>
       </c>
       <c r="G17" t="s">
         <v>44</v>
@@ -2626,7 +2804,7 @@
       </c>
       <c r="I17" s="5"/>
       <c r="J17" s="5">
-        <v>0.6726000000000001</v>
+        <v>0.7592</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
@@ -2643,10 +2821,10 @@
         <v>4799121512</v>
       </c>
       <c r="E18" s="1">
-        <v>12929826184</v>
+        <v>14884833807</v>
       </c>
       <c r="F18" s="7">
-        <v>-2713341437</v>
+        <v>1955007623</v>
       </c>
       <c r="G18" t="s">
         <v>44</v>
@@ -2656,7 +2834,7 @@
       </c>
       <c r="I18" s="5"/>
       <c r="J18" s="5">
-        <v>0.1998</v>
+        <v>0.2047</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -2673,10 +2851,10 @@
         <v>3601238896</v>
       </c>
       <c r="E19" s="1">
-        <v>7926139191</v>
+        <v>8789605075</v>
       </c>
       <c r="F19" s="7">
-        <v>-929727263</v>
+        <v>863465884</v>
       </c>
       <c r="G19" t="s">
         <v>44</v>
@@ -2686,7 +2864,7 @@
       </c>
       <c r="I19" s="5"/>
       <c r="J19" s="5">
-        <v>0.1998</v>
+        <v>0.2047</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -2703,10 +2881,10 @@
         <v>15088712403</v>
       </c>
       <c r="E20" s="1">
-        <v>44447329187</v>
+        <v>50771177760</v>
       </c>
       <c r="F20" s="7">
-        <v>-6906662932</v>
+        <v>6323848573</v>
       </c>
       <c r="G20" t="s">
         <v>44</v>
@@ -2716,7 +2894,7 @@
       </c>
       <c r="I20" s="5"/>
       <c r="J20" s="5">
-        <v>0.21</v>
+        <v>0.2148</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -2733,10 +2911,10 @@
         <v>5018453600</v>
       </c>
       <c r="E21" s="1">
-        <v>12530478206</v>
+        <v>14312952245</v>
       </c>
       <c r="F21" s="7">
-        <v>-2176158615</v>
+        <v>1782474039</v>
       </c>
       <c r="G21" t="s">
         <v>44</v>
@@ -2746,7 +2924,7 @@
       </c>
       <c r="I21" s="5"/>
       <c r="J21" s="5">
-        <v>0.21</v>
+        <v>0.2148</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -2763,10 +2941,10 @@
         <v>6382621945</v>
       </c>
       <c r="E22" s="1">
-        <v>13603740058</v>
+        <v>15279052882</v>
       </c>
       <c r="F22" s="7">
-        <v>-2277975695</v>
+        <v>1675312824</v>
       </c>
       <c r="G22" t="s">
         <v>44</v>
@@ -2776,7 +2954,7 @@
       </c>
       <c r="I22" s="5"/>
       <c r="J22" s="5">
-        <v>0.21</v>
+        <v>0.2148</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -2793,10 +2971,10 @@
         <v>7096535878</v>
       </c>
       <c r="E23" s="1">
-        <v>17348896195</v>
+        <v>19706122817</v>
       </c>
       <c r="F23" s="7">
-        <v>-1941207021</v>
+        <v>2357226622</v>
       </c>
       <c r="G23" t="s">
         <v>44</v>
@@ -2806,7 +2984,7 @@
       </c>
       <c r="I23" s="5"/>
       <c r="J23" s="5">
-        <v>0.21</v>
+        <v>0.2148</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -2823,10 +3001,10 @@
         <v>8254694051</v>
       </c>
       <c r="E24" s="1">
-        <v>25518246126</v>
+        <v>27620326545</v>
       </c>
       <c r="F24" s="7">
-        <v>-2042873014</v>
+        <v>2102080419</v>
       </c>
       <c r="G24" t="s">
         <v>44</v>
@@ -2836,7 +3014,7 @@
       </c>
       <c r="I24" s="5"/>
       <c r="J24" s="5">
-        <v>2.0934</v>
+        <v>2.3571</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -2853,10 +3031,10 @@
         <v>12775472416</v>
       </c>
       <c r="E25" s="1">
-        <v>40249195792</v>
+        <v>44009858884</v>
       </c>
       <c r="F25" s="7">
-        <v>-3720168503</v>
+        <v>3760663092</v>
       </c>
       <c r="G25" t="s">
         <v>44</v>
@@ -2866,7 +3044,7 @@
       </c>
       <c r="I25" s="5"/>
       <c r="J25" s="5">
-        <v>2.0934</v>
+        <v>2.3571</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -2883,10 +3061,10 @@
         <v>9403481285</v>
       </c>
       <c r="E26" s="1">
-        <v>29896625207</v>
+        <v>32517210660</v>
       </c>
       <c r="F26" s="7">
-        <v>-2561695490</v>
+        <v>2620585453</v>
       </c>
       <c r="G26" t="s">
         <v>44</v>
@@ -2896,7 +3074,7 @@
       </c>
       <c r="I26" s="5"/>
       <c r="J26" s="5">
-        <v>2.0934</v>
+        <v>2.3571</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
@@ -2913,10 +3091,10 @@
         <v>12635490783</v>
       </c>
       <c r="E27" s="1">
-        <v>39498492066</v>
+        <v>42818475870</v>
       </c>
       <c r="F27" s="7">
-        <v>-3193640300</v>
+        <v>3319983804</v>
       </c>
       <c r="G27" t="s">
         <v>44</v>
@@ -2926,7 +3104,7 @@
       </c>
       <c r="I27" s="5"/>
       <c r="J27" s="5">
-        <v>2.0934</v>
+        <v>2.3571</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -2943,10 +3121,10 @@
         <v>10445956159</v>
       </c>
       <c r="E28" s="1">
-        <v>33972525542</v>
+        <v>36750872629</v>
       </c>
       <c r="F28" s="7">
-        <v>-2547162188</v>
+        <v>2778347087</v>
       </c>
       <c r="G28" t="s">
         <v>44</v>
@@ -2956,7 +3134,7 @@
       </c>
       <c r="I28" s="5"/>
       <c r="J28" s="5">
-        <v>2.0934</v>
+        <v>2.3571</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -2973,10 +3151,10 @@
         <v>7235716436</v>
       </c>
       <c r="E29" s="1">
-        <v>22662104792</v>
+        <v>24682847745</v>
       </c>
       <c r="F29" s="7">
-        <v>-1941110779</v>
+        <v>2020742953</v>
       </c>
       <c r="G29" t="s">
         <v>44</v>
@@ -2986,7 +3164,7 @@
       </c>
       <c r="I29" s="5"/>
       <c r="J29" s="5">
-        <v>2.0934</v>
+        <v>2.3571</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -3003,10 +3181,10 @@
         <v>4439275178</v>
       </c>
       <c r="E30" s="1">
-        <v>14479782645</v>
+        <v>15816536859</v>
       </c>
       <c r="F30" s="7">
-        <v>-1187939432</v>
+        <v>1336754214</v>
       </c>
       <c r="G30" t="s">
         <v>44</v>
@@ -3016,7 +3194,7 @@
       </c>
       <c r="I30" s="5"/>
       <c r="J30" s="5">
-        <v>2.0934</v>
+        <v>2.3571</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -3033,10 +3211,10 @@
         <v>13613817760</v>
       </c>
       <c r="E31" s="1">
-        <v>30231598199</v>
+        <v>34549877118</v>
       </c>
       <c r="F31" s="7">
-        <v>-4727899740</v>
+        <v>4318278919</v>
       </c>
       <c r="G31" t="s">
         <v>44</v>
@@ -3046,7 +3224,7 @@
       </c>
       <c r="I31" s="5"/>
       <c r="J31" s="5">
-        <v>0.1286</v>
+        <v>0.1335</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -3063,10 +3241,10 @@
         <v>11400361947</v>
       </c>
       <c r="E32" s="1">
-        <v>30148968555</v>
+        <v>37022292862</v>
       </c>
       <c r="F32" s="7">
-        <v>-4683153126</v>
+        <v>6873324307</v>
       </c>
       <c r="G32" t="s">
         <v>44</v>
@@ -3076,7 +3254,7 @@
       </c>
       <c r="I32" s="5"/>
       <c r="J32" s="5">
-        <v>0.1286</v>
+        <v>0.1335</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -3093,10 +3271,10 @@
         <v>13638402860</v>
       </c>
       <c r="E33" s="1">
-        <v>28605010963</v>
+        <v>33625784029</v>
       </c>
       <c r="F33" s="7">
-        <v>-5936009054</v>
+        <v>5020773066</v>
       </c>
       <c r="G33" t="s">
         <v>44</v>
@@ -3106,7 +3284,7 @@
       </c>
       <c r="I33" s="5"/>
       <c r="J33" s="5">
-        <v>0.1286</v>
+        <v>0.1335</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -3123,10 +3301,10 @@
         <v>20601693072</v>
       </c>
       <c r="E34" s="1">
-        <v>56940962295</v>
+        <v>73879997576</v>
       </c>
       <c r="F34" s="7">
-        <v>-8643495963</v>
+        <v>16939035281</v>
       </c>
       <c r="G34" t="s">
         <v>44</v>
@@ -3136,7 +3314,7 @@
       </c>
       <c r="I34" s="5"/>
       <c r="J34" s="5">
-        <v>0.1286</v>
+        <v>0.1335</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -3153,10 +3331,10 @@
         <v>19457627824</v>
       </c>
       <c r="E35" s="1">
-        <v>42021514983</v>
+        <v>49975642929</v>
       </c>
       <c r="F35" s="7">
-        <v>-4491313504</v>
+        <v>7954127946</v>
       </c>
       <c r="G35" t="s">
         <v>44</v>
@@ -3166,7 +3344,7 @@
       </c>
       <c r="I35" s="5"/>
       <c r="J35" s="5">
-        <v>0.1286</v>
+        <v>0.1335</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -3183,10 +3361,10 @@
         <v>9724896734</v>
       </c>
       <c r="E36" s="1">
-        <v>21096859167</v>
+        <v>24396971507</v>
       </c>
       <c r="F36" s="7">
-        <v>-4447073144</v>
+        <v>3300112340</v>
       </c>
       <c r="G36" t="s">
         <v>44</v>
@@ -3196,7 +3374,7 @@
       </c>
       <c r="I36" s="5"/>
       <c r="J36" s="5">
-        <v>0.1286</v>
+        <v>0.1335</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -3213,10 +3391,10 @@
         <v>17743902371</v>
       </c>
       <c r="E37" s="1">
-        <v>16416991185</v>
+        <v>18727863428</v>
       </c>
       <c r="F37" s="7">
-        <v>-1858941707</v>
+        <v>2310872243</v>
       </c>
       <c r="G37" t="s">
         <v>44</v>
@@ -3226,7 +3404,7 @@
       </c>
       <c r="I37" s="5"/>
       <c r="J37" s="5">
-        <v>0.013600000000000001</v>
+        <v>0.0189</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -3243,10 +3421,10 @@
         <v>25118214883</v>
       </c>
       <c r="E38" s="1">
-        <v>22752979420</v>
+        <v>25971349161</v>
       </c>
       <c r="F38" s="7">
-        <v>-3714805833</v>
+        <v>3218369741</v>
       </c>
       <c r="G38" t="s">
         <v>44</v>
@@ -3256,7 +3434,7 @@
       </c>
       <c r="I38" s="5"/>
       <c r="J38" s="5">
-        <v>0.013600000000000001</v>
+        <v>0.0189</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
@@ -3273,10 +3451,10 @@
         <v>18706659825</v>
       </c>
       <c r="E39" s="1">
-        <v>16064777486</v>
+        <v>18699763809</v>
       </c>
       <c r="F39" s="7">
-        <v>-3367153763</v>
+        <v>2634986323</v>
       </c>
       <c r="G39" t="s">
         <v>44</v>
@@ -3286,7 +3464,7 @@
       </c>
       <c r="I39" s="5"/>
       <c r="J39" s="5">
-        <v>0.013600000000000001</v>
+        <v>0.0189</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
@@ -3303,10 +3481,10 @@
         <v>23159171521</v>
       </c>
       <c r="E40" s="1">
-        <v>21117075101</v>
+        <v>24364459351</v>
       </c>
       <c r="F40" s="7">
-        <v>-3106908113</v>
+        <v>3247384250</v>
       </c>
       <c r="G40" t="s">
         <v>44</v>
@@ -3316,7 +3494,7 @@
       </c>
       <c r="I40" s="5"/>
       <c r="J40" s="5">
-        <v>0.013600000000000001</v>
+        <v>0.0189</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
@@ -3333,10 +3511,10 @@
         <v>34803007809</v>
       </c>
       <c r="E41" s="1">
-        <v>30727399354</v>
+        <v>38933092424</v>
       </c>
       <c r="F41" s="7">
-        <v>-4182581585</v>
+        <v>8205693070</v>
       </c>
       <c r="G41" t="s">
         <v>44</v>
@@ -3346,7 +3524,7 @@
       </c>
       <c r="I41" s="5"/>
       <c r="J41" s="5">
-        <v>0.013600000000000001</v>
+        <v>0.0189</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -3363,10 +3541,10 @@
         <v>3000000000</v>
       </c>
       <c r="E42" s="1">
-        <v>7088003475</v>
+        <v>7761837386</v>
       </c>
       <c r="F42" s="7">
-        <v>-1031036926</v>
+        <v>673833911</v>
       </c>
       <c r="G42" t="s">
         <v>44</v>
@@ -3376,7 +3554,7 @@
       </c>
       <c r="I42" s="5"/>
       <c r="J42" s="5">
-        <v>1.2554</v>
+        <v>1.4536000000000002</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
@@ -3393,10 +3571,10 @@
         <v>3000000000</v>
       </c>
       <c r="E43" s="1">
-        <v>7046409838</v>
+        <v>7666300351</v>
       </c>
       <c r="F43" s="7">
-        <v>-960398939</v>
+        <v>619890513</v>
       </c>
       <c r="G43" t="s">
         <v>44</v>
@@ -3406,7 +3584,7 @@
       </c>
       <c r="I43" s="5"/>
       <c r="J43" s="5">
-        <v>1.2554</v>
+        <v>1.4536000000000002</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
@@ -3423,10 +3601,10 @@
         <v>3000000000</v>
       </c>
       <c r="E44" s="1">
-        <v>7058698601</v>
+        <v>7724080509</v>
       </c>
       <c r="F44" s="7">
-        <v>-1084168934</v>
+        <v>665381908</v>
       </c>
       <c r="G44" t="s">
         <v>44</v>
@@ -3436,7 +3614,7 @@
       </c>
       <c r="I44" s="5"/>
       <c r="J44" s="5">
-        <v>1.2554</v>
+        <v>1.4536000000000002</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
@@ -3453,10 +3631,10 @@
         <v>3000000000</v>
       </c>
       <c r="E45" s="1">
-        <v>7299682641</v>
+        <v>7902740243</v>
       </c>
       <c r="F45" s="7">
-        <v>-1048120932</v>
+        <v>603057602</v>
       </c>
       <c r="G45" t="s">
         <v>44</v>
@@ -3466,7 +3644,7 @@
       </c>
       <c r="I45" s="5"/>
       <c r="J45" s="5">
-        <v>1.2554</v>
+        <v>1.4536000000000002</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
@@ -3483,10 +3661,10 @@
         <v>3000000000</v>
       </c>
       <c r="E46" s="1">
-        <v>6973552798</v>
+        <v>7748837585</v>
       </c>
       <c r="F46" s="7">
-        <v>-1133900852</v>
+        <v>775284787</v>
       </c>
       <c r="G46" t="s">
         <v>44</v>
@@ -3496,7 +3674,7 @@
       </c>
       <c r="I46" s="5"/>
       <c r="J46" s="5">
-        <v>1.2554</v>
+        <v>1.4536000000000002</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
@@ -3513,10 +3691,10 @@
         <v>8000000000</v>
       </c>
       <c r="E47" s="1">
-        <v>21201075224</v>
+        <v>24224834632</v>
       </c>
       <c r="F47" s="7">
-        <v>-3302151519</v>
+        <v>3023759408</v>
       </c>
       <c r="G47" t="s">
         <v>44</v>
@@ -3526,7 +3704,7 @@
       </c>
       <c r="I47" s="5"/>
       <c r="J47" s="5">
-        <v>0.2808</v>
+        <v>0.2857</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
@@ -3543,10 +3721,10 @@
         <v>8000000000</v>
       </c>
       <c r="E48" s="1">
-        <v>16562402836</v>
+        <v>19219973338</v>
       </c>
       <c r="F48" s="7">
-        <v>-3285455291</v>
+        <v>2657570502</v>
       </c>
       <c r="G48" t="s">
         <v>44</v>
@@ -3556,7 +3734,7 @@
       </c>
       <c r="I48" s="5"/>
       <c r="J48" s="5">
-        <v>0.2808</v>
+        <v>0.2857</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
@@ -3573,10 +3751,10 @@
         <v>8000000000</v>
       </c>
       <c r="E49" s="1">
-        <v>20580006389</v>
+        <v>24570018459</v>
       </c>
       <c r="F49" s="7">
-        <v>-2300995758</v>
+        <v>3990012070</v>
       </c>
       <c r="G49" t="s">
         <v>44</v>
@@ -3586,7 +3764,7 @@
       </c>
       <c r="I49" s="5"/>
       <c r="J49" s="5">
-        <v>0.2808</v>
+        <v>0.2857</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
@@ -3603,10 +3781,10 @@
         <v>8000000000</v>
       </c>
       <c r="E50" s="1">
-        <v>17031604335</v>
+        <v>19854566007</v>
       </c>
       <c r="F50" s="7">
-        <v>-4051602044</v>
+        <v>2822961672</v>
       </c>
       <c r="G50" t="s">
         <v>44</v>
@@ -3616,7 +3794,7 @@
       </c>
       <c r="I50" s="5"/>
       <c r="J50" s="5">
-        <v>0.2808</v>
+        <v>0.2857</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
@@ -3633,10 +3811,10 @@
         <v>8000000000</v>
       </c>
       <c r="E51" s="1">
-        <v>24613117899</v>
+        <v>31434344914</v>
       </c>
       <c r="F51" s="7">
-        <v>-3391873397</v>
+        <v>6821227015</v>
       </c>
       <c r="G51" t="s">
         <v>44</v>
@@ -3646,7 +3824,7 @@
       </c>
       <c r="I51" s="5"/>
       <c r="J51" s="5">
-        <v>0.2808</v>
+        <v>0.2857</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
@@ -3663,10 +3841,10 @@
         <v>8000000000</v>
       </c>
       <c r="E52" s="1">
-        <v>21079896694</v>
+        <v>25091454446</v>
       </c>
       <c r="F52" s="7">
-        <v>-3866696231</v>
+        <v>4011557752</v>
       </c>
       <c r="G52" t="s">
         <v>44</v>
@@ -3676,7 +3854,7 @@
       </c>
       <c r="I52" s="5"/>
       <c r="J52" s="5">
-        <v>0.2808</v>
+        <v>0.2857</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
@@ -3693,10 +3871,10 @@
         <v>7000000000</v>
       </c>
       <c r="E53" s="1">
-        <v>12706419190</v>
+        <v>14133982001</v>
       </c>
       <c r="F53" s="7">
-        <v>-1482204945</v>
+        <v>1427562811</v>
       </c>
       <c r="G53" t="s">
         <v>44</v>
@@ -3706,7 +3884,7 @@
       </c>
       <c r="I53" s="5"/>
       <c r="J53" s="5">
-        <v>0.1681</v>
+        <v>0.1729</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
@@ -3723,10 +3901,10 @@
         <v>7000000000</v>
       </c>
       <c r="E54" s="1">
-        <v>18530231676</v>
+        <v>22660503311</v>
       </c>
       <c r="F54" s="7">
-        <v>-2892118189</v>
+        <v>4130271635</v>
       </c>
       <c r="G54" t="s">
         <v>44</v>
@@ -3736,7 +3914,7 @@
       </c>
       <c r="I54" s="5"/>
       <c r="J54" s="5">
-        <v>0.1681</v>
+        <v>0.1729</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
@@ -3753,10 +3931,10 @@
         <v>7000000000</v>
       </c>
       <c r="E55" s="1">
-        <v>15293632896</v>
+        <v>17678683542</v>
       </c>
       <c r="F55" s="7">
-        <v>-3134839058</v>
+        <v>2385050646</v>
       </c>
       <c r="G55" t="s">
         <v>44</v>
@@ -3766,7 +3944,7 @@
       </c>
       <c r="I55" s="5"/>
       <c r="J55" s="5">
-        <v>0.1681</v>
+        <v>0.1729</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
@@ -3783,10 +3961,10 @@
         <v>7000000000</v>
       </c>
       <c r="E56" s="1">
-        <v>15089595873</v>
+        <v>17589517587</v>
       </c>
       <c r="F56" s="7">
-        <v>-3597316692</v>
+        <v>2499921714</v>
       </c>
       <c r="G56" t="s">
         <v>44</v>
@@ -3796,7 +3974,7 @@
       </c>
       <c r="I56" s="5"/>
       <c r="J56" s="5">
-        <v>0.1681</v>
+        <v>0.1729</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
@@ -3813,10 +3991,10 @@
         <v>7000000000</v>
       </c>
       <c r="E57" s="1">
-        <v>19452951069</v>
+        <v>25283605176</v>
       </c>
       <c r="F57" s="7">
-        <v>-2986864821</v>
+        <v>5830654107</v>
       </c>
       <c r="G57" t="s">
         <v>44</v>
@@ -3826,7 +4004,7 @@
       </c>
       <c r="I57" s="5"/>
       <c r="J57" s="5">
-        <v>0.1681</v>
+        <v>0.1729</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
@@ -3843,10 +4021,10 @@
         <v>7000000000</v>
       </c>
       <c r="E58" s="1">
-        <v>9121413882</v>
+        <v>10889639888</v>
       </c>
       <c r="F58" s="7">
-        <v>-3054589966</v>
+        <v>1768226006</v>
       </c>
       <c r="G58" t="s">
         <v>44</v>
@@ -3856,7 +4034,7 @@
       </c>
       <c r="I58" s="5"/>
       <c r="J58" s="5">
-        <v>0.1681</v>
+        <v>0.1729</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
@@ -3873,10 +4051,10 @@
         <v>7000000000</v>
       </c>
       <c r="E59" s="1">
-        <v>14552780847</v>
+        <v>16452459633</v>
       </c>
       <c r="F59" s="7">
-        <v>-1793710777</v>
+        <v>1899678786</v>
       </c>
       <c r="G59" t="s">
         <v>44</v>
@@ -3886,7 +4064,7 @@
       </c>
       <c r="I59" s="5"/>
       <c r="J59" s="5">
-        <v>0.1681</v>
+        <v>0.1729</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
@@ -3903,10 +4081,10 @@
         <v>9000000000</v>
       </c>
       <c r="E60" s="1">
-        <v>13507194558</v>
+        <v>14732259184</v>
       </c>
       <c r="F60" s="7">
-        <v>2841307175</v>
+        <v>1225064626</v>
       </c>
       <c r="G60" t="s">
         <v>44</v>
@@ -3916,7 +4094,7 @@
       </c>
       <c r="I60" s="5"/>
       <c r="J60" s="5">
-        <v>1.1673</v>
+        <v>1.3219</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
@@ -3933,10 +4111,10 @@
         <v>9000000000</v>
       </c>
       <c r="E61" s="1">
-        <v>12874751853</v>
+        <v>13537552457</v>
       </c>
       <c r="F61" s="7">
-        <v>3138260899</v>
+        <v>662800604</v>
       </c>
       <c r="G61" t="s">
         <v>44</v>
@@ -3946,7 +4124,7 @@
       </c>
       <c r="I61" s="5"/>
       <c r="J61" s="5">
-        <v>1.1673</v>
+        <v>1.3219</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
@@ -3963,10 +4141,10 @@
         <v>9000000000</v>
       </c>
       <c r="E62" s="1">
-        <v>13017408018</v>
+        <v>13984059027</v>
       </c>
       <c r="F62" s="7">
-        <v>2815123461</v>
+        <v>966651009</v>
       </c>
       <c r="G62" t="s">
         <v>44</v>
@@ -3976,7 +4154,7 @@
       </c>
       <c r="I62" s="5"/>
       <c r="J62" s="5">
-        <v>1.1673</v>
+        <v>1.3219</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
@@ -3993,10 +4171,10 @@
         <v>9000000000</v>
       </c>
       <c r="E63" s="1">
-        <v>12735007874</v>
+        <v>13949037170</v>
       </c>
       <c r="F63" s="7">
-        <v>2937317022</v>
+        <v>1214029296</v>
       </c>
       <c r="G63" t="s">
         <v>44</v>
@@ -4006,7 +4184,7 @@
       </c>
       <c r="I63" s="5"/>
       <c r="J63" s="5">
-        <v>1.1673</v>
+        <v>1.3219</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
@@ -4023,10 +4201,10 @@
         <v>9000000000</v>
       </c>
       <c r="E64" s="1">
-        <v>12823234724</v>
+        <v>13898271601</v>
       </c>
       <c r="F64" s="7">
-        <v>3025246858</v>
+        <v>1075036877</v>
       </c>
       <c r="G64" t="s">
         <v>44</v>
@@ -4036,7 +4214,7 @@
       </c>
       <c r="I64" s="5"/>
       <c r="J64" s="5">
-        <v>1.1673</v>
+        <v>1.3219</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
@@ -4053,10 +4231,10 @@
         <v>9000000000</v>
       </c>
       <c r="E65" s="1">
-        <v>12903392256</v>
+        <v>13943010448</v>
       </c>
       <c r="F65" s="7">
-        <v>2886045448</v>
+        <v>1039618192</v>
       </c>
       <c r="G65" t="s">
         <v>44</v>
@@ -4066,7 +4244,7 @@
       </c>
       <c r="I65" s="5"/>
       <c r="J65" s="5">
-        <v>1.1673</v>
+        <v>1.3219</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
@@ -4083,10 +4261,10 @@
         <v>9000000000</v>
       </c>
       <c r="E66" s="1">
-        <v>12279463586</v>
+        <v>14022640413</v>
       </c>
       <c r="F66" s="7">
-        <v>-1996133443</v>
+        <v>1743176827</v>
       </c>
       <c r="G66" t="s">
         <v>44</v>
@@ -4096,7 +4274,7 @@
       </c>
       <c r="I66" s="5"/>
       <c r="J66" s="5">
-        <v>0.0444</v>
+        <v>0.049699999999999994</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
@@ -4113,10 +4291,10 @@
         <v>9000000000</v>
       </c>
       <c r="E67" s="1">
-        <v>13053425511</v>
+        <v>14558557114</v>
       </c>
       <c r="F67" s="7">
-        <v>-1809935991</v>
+        <v>1505131603</v>
       </c>
       <c r="G67" t="s">
         <v>44</v>
@@ -4126,7 +4304,7 @@
       </c>
       <c r="I67" s="5"/>
       <c r="J67" s="5">
-        <v>0.0444</v>
+        <v>0.049699999999999994</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
@@ -4143,10 +4321,10 @@
         <v>9000000000</v>
       </c>
       <c r="E68" s="1">
-        <v>13497748336</v>
+        <v>16409783221</v>
       </c>
       <c r="F68" s="7">
-        <v>-2075471315</v>
+        <v>2912034885</v>
       </c>
       <c r="G68" t="s">
         <v>44</v>
@@ -4156,7 +4334,7 @@
       </c>
       <c r="I68" s="5"/>
       <c r="J68" s="5">
-        <v>0.0444</v>
+        <v>0.049699999999999994</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
@@ -4173,10 +4351,10 @@
         <v>9000000000</v>
       </c>
       <c r="E69" s="1">
-        <v>12623775612</v>
+        <v>15802586707</v>
       </c>
       <c r="F69" s="7">
-        <v>-2086726212</v>
+        <v>3178811095</v>
       </c>
       <c r="G69" t="s">
         <v>44</v>
@@ -4186,7 +4364,7 @@
       </c>
       <c r="I69" s="5"/>
       <c r="J69" s="5">
-        <v>0.0444</v>
+        <v>0.049699999999999994</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
@@ -4203,10 +4381,10 @@
         <v>9000000000</v>
       </c>
       <c r="E70" s="1">
-        <v>13042654095</v>
+        <v>14767488219</v>
       </c>
       <c r="F70" s="7">
-        <v>-1703940444</v>
+        <v>1724834124</v>
       </c>
       <c r="G70" t="s">
         <v>44</v>
@@ -4216,7 +4394,7 @@
       </c>
       <c r="I70" s="5"/>
       <c r="J70" s="5">
-        <v>0.0444</v>
+        <v>0.049699999999999994</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
@@ -4233,10 +4411,10 @@
         <v>5000000000</v>
       </c>
       <c r="E71" s="1">
-        <v>4902240425</v>
+        <v>5191420651</v>
       </c>
       <c r="F71" s="7">
-        <v>3357707657</v>
+        <v>289180226</v>
       </c>
       <c r="G71" t="s">
         <v>44</v>
@@ -4245,26 +4423,28 @@
         <v>45</v>
       </c>
       <c r="I71" s="5"/>
-      <c r="J71" s="5"/>
+      <c r="J71" s="5">
+        <v>0.0143</v>
+      </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B72" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C72" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D72" s="1">
-        <v>15603507854</v>
+        <v>5000000000</v>
       </c>
       <c r="E72" s="1">
-        <v>32320138788</v>
+        <v>5277089640</v>
       </c>
       <c r="F72" s="7">
-        <v>-6039242500</v>
+        <v>5277089640</v>
       </c>
       <c r="G72" t="s">
         <v>44</v>
@@ -4274,27 +4454,27 @@
       </c>
       <c r="I72" s="5"/>
       <c r="J72" s="5">
-        <v>0.0947</v>
+        <v>0.0143</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B73" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C73" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D73" s="1">
-        <v>13492877440</v>
+        <v>5000000000</v>
       </c>
       <c r="E73" s="1">
-        <v>26790911817</v>
+        <v>5793806236</v>
       </c>
       <c r="F73" s="7">
-        <v>-5561557655</v>
+        <v>5793806236</v>
       </c>
       <c r="G73" t="s">
         <v>44</v>
@@ -4304,27 +4484,27 @@
       </c>
       <c r="I73" s="5"/>
       <c r="J73" s="5">
-        <v>0.0947</v>
+        <v>0.0143</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B74" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C74" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="D74" s="1">
-        <v>6530798735</v>
+        <v>5000000000</v>
       </c>
       <c r="E74" s="1">
-        <v>13425179562</v>
+        <v>5706018434</v>
       </c>
       <c r="F74" s="7">
-        <v>-918698815</v>
+        <v>5706018434</v>
       </c>
       <c r="G74" t="s">
         <v>44</v>
@@ -4334,27 +4514,27 @@
       </c>
       <c r="I74" s="5"/>
       <c r="J74" s="5">
-        <v>0.9778</v>
+        <v>0.0143</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B75" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C75" t="s">
-        <v>43</v>
+        <v>77</v>
       </c>
       <c r="D75" s="1">
-        <v>27357530009</v>
+        <v>5000000000</v>
       </c>
       <c r="E75" s="1">
-        <v>78465559204</v>
+        <v>5596824881</v>
       </c>
       <c r="F75" s="7">
-        <v>-11765906915</v>
+        <v>5596824881</v>
       </c>
       <c r="G75" t="s">
         <v>44</v>
@@ -4364,7 +4544,7 @@
       </c>
       <c r="I75" s="5"/>
       <c r="J75" s="5">
-        <v>0.132</v>
+        <v>0.0143</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
@@ -4372,19 +4552,19 @@
         <v>6</v>
       </c>
       <c r="B76" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C76" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="D76" s="1">
-        <v>4800107976</v>
+        <v>15603507854</v>
       </c>
       <c r="E76" s="1">
-        <v>12931832350</v>
+        <v>38523549736</v>
       </c>
       <c r="F76" s="7">
-        <v>-2713291289</v>
+        <v>6203410948</v>
       </c>
       <c r="G76" t="s">
         <v>44</v>
@@ -4394,7 +4574,7 @@
       </c>
       <c r="I76" s="5"/>
       <c r="J76" s="5">
-        <v>0.1998</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
@@ -4402,19 +4582,19 @@
         <v>6</v>
       </c>
       <c r="B77" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C77" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D77" s="1">
-        <v>2601947821</v>
+        <v>13492877440</v>
       </c>
       <c r="E77" s="1">
-        <v>6928377916</v>
+        <v>31506916668</v>
       </c>
       <c r="F77" s="7">
-        <v>-898102998</v>
+        <v>4716004851</v>
       </c>
       <c r="G77" t="s">
         <v>44</v>
@@ -4424,7 +4604,7 @@
       </c>
       <c r="I77" s="5"/>
       <c r="J77" s="5">
-        <v>0.1998</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
@@ -4432,19 +4612,19 @@
         <v>6</v>
       </c>
       <c r="B78" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C78" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D78" s="1">
-        <v>15089937312</v>
+        <v>6530798735</v>
       </c>
       <c r="E78" s="1">
-        <v>44451751213</v>
+        <v>14445581832</v>
       </c>
       <c r="F78" s="7">
-        <v>-6906493455</v>
+        <v>1020402270</v>
       </c>
       <c r="G78" t="s">
         <v>44</v>
@@ -4454,7 +4634,7 @@
       </c>
       <c r="I78" s="5"/>
       <c r="J78" s="5">
-        <v>0.21</v>
+        <v>1.1189</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
@@ -4462,19 +4642,19 @@
         <v>6</v>
       </c>
       <c r="B79" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C79" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="D79" s="1">
-        <v>3019107110</v>
+        <v>27357530009</v>
       </c>
       <c r="E79" s="1">
-        <v>10627945460</v>
+        <v>101691766200</v>
       </c>
       <c r="F79" s="7">
-        <v>-1827363987</v>
+        <v>23226206996</v>
       </c>
       <c r="G79" t="s">
         <v>44</v>
@@ -4484,7 +4664,7 @@
       </c>
       <c r="I79" s="5"/>
       <c r="J79" s="5">
-        <v>0.21</v>
+        <v>0.1368</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
@@ -4492,19 +4672,19 @@
         <v>6</v>
       </c>
       <c r="B80" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C80" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="D80" s="1">
-        <v>4384957618</v>
+        <v>4800107976</v>
       </c>
       <c r="E80" s="1">
-        <v>11811294891</v>
+        <v>14886892642</v>
       </c>
       <c r="F80" s="7">
-        <v>-1980272675</v>
+        <v>1955060292</v>
       </c>
       <c r="G80" t="s">
         <v>44</v>
@@ -4514,7 +4694,7 @@
       </c>
       <c r="I80" s="5"/>
       <c r="J80" s="5">
-        <v>0.21</v>
+        <v>0.2047</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
@@ -4522,19 +4702,19 @@
         <v>6</v>
       </c>
       <c r="B81" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C81" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D81" s="1">
-        <v>5597524598</v>
+        <v>2601947821</v>
       </c>
       <c r="E81" s="1">
-        <v>15904763483</v>
+        <v>7757776290</v>
       </c>
       <c r="F81" s="7">
-        <v>-1781367234</v>
+        <v>829398374</v>
       </c>
       <c r="G81" t="s">
         <v>44</v>
@@ -4544,7 +4724,7 @@
       </c>
       <c r="I81" s="5"/>
       <c r="J81" s="5">
-        <v>0.21</v>
+        <v>0.2047</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
@@ -4552,19 +4732,19 @@
         <v>6</v>
       </c>
       <c r="B82" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C82" t="s">
         <v>60</v>
       </c>
       <c r="D82" s="1">
-        <v>1000000000</v>
+        <v>15089937312</v>
       </c>
       <c r="E82" s="1">
-        <v>2330215349</v>
+        <v>50775773672</v>
       </c>
       <c r="F82" s="7">
-        <v>-376471490</v>
+        <v>6324022459</v>
       </c>
       <c r="G82" t="s">
         <v>44</v>
@@ -4574,7 +4754,7 @@
       </c>
       <c r="I82" s="5"/>
       <c r="J82" s="5">
-        <v>1.2554</v>
+        <v>0.2148</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
@@ -4582,19 +4762,19 @@
         <v>6</v>
       </c>
       <c r="B83" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C83" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D83" s="1">
-        <v>1000000000</v>
+        <v>3019107110</v>
       </c>
       <c r="E83" s="1">
-        <v>2302140221</v>
+        <v>12207646533</v>
       </c>
       <c r="F83" s="7">
-        <v>-367060392</v>
+        <v>1579701073</v>
       </c>
       <c r="G83" t="s">
         <v>44</v>
@@ -4604,7 +4784,7 @@
       </c>
       <c r="I83" s="5"/>
       <c r="J83" s="5">
-        <v>1.2554</v>
+        <v>0.2148</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
@@ -4612,19 +4792,19 @@
         <v>6</v>
       </c>
       <c r="B84" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C84" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="D84" s="1">
-        <v>1000000000</v>
+        <v>4384957618</v>
       </c>
       <c r="E84" s="1">
-        <v>2297488877</v>
+        <v>13267835617</v>
       </c>
       <c r="F84" s="7">
-        <v>-417079026</v>
+        <v>1456540726</v>
       </c>
       <c r="G84" t="s">
         <v>44</v>
@@ -4634,7 +4814,7 @@
       </c>
       <c r="I84" s="5"/>
       <c r="J84" s="5">
-        <v>1.2554</v>
+        <v>0.2148</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
@@ -4642,19 +4822,19 @@
         <v>6</v>
       </c>
       <c r="B85" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C85" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="D85" s="1">
-        <v>1000000000</v>
+        <v>5597524598</v>
       </c>
       <c r="E85" s="1">
-        <v>2374031106</v>
+        <v>18069233307</v>
       </c>
       <c r="F85" s="7">
-        <v>-408884808</v>
+        <v>2164469824</v>
       </c>
       <c r="G85" t="s">
         <v>44</v>
@@ -4664,7 +4844,7 @@
       </c>
       <c r="I85" s="5"/>
       <c r="J85" s="5">
-        <v>1.2554</v>
+        <v>0.2148</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
@@ -4675,16 +4855,16 @@
         <v>87</v>
       </c>
       <c r="C86" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D86" s="1">
-        <v>1000000000</v>
+        <v>3000000000</v>
       </c>
       <c r="E86" s="1">
-        <v>2293703108</v>
+        <v>6032526706</v>
       </c>
       <c r="F86" s="7">
-        <v>-409648800</v>
+        <v>637177959</v>
       </c>
       <c r="G86" t="s">
         <v>44</v>
@@ -4694,7 +4874,7 @@
       </c>
       <c r="I86" s="5"/>
       <c r="J86" s="5">
-        <v>1.2554</v>
+        <v>0.1729</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
@@ -4702,19 +4882,19 @@
         <v>6</v>
       </c>
       <c r="B87" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C87" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="D87" s="1">
         <v>3000000000</v>
       </c>
       <c r="E87" s="1">
-        <v>5395348747</v>
+        <v>9541399095</v>
       </c>
       <c r="F87" s="7">
-        <v>-655239852</v>
+        <v>1738696867</v>
       </c>
       <c r="G87" t="s">
         <v>44</v>
@@ -4724,7 +4904,7 @@
       </c>
       <c r="I87" s="5"/>
       <c r="J87" s="5">
-        <v>0.1681</v>
+        <v>0.1729</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
@@ -4732,19 +4912,19 @@
         <v>6</v>
       </c>
       <c r="B88" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C88" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="D88" s="1">
         <v>3000000000</v>
       </c>
       <c r="E88" s="1">
-        <v>7802702228</v>
+        <v>7530376964</v>
       </c>
       <c r="F88" s="7">
-        <v>-1217848671</v>
+        <v>1016918926</v>
       </c>
       <c r="G88" t="s">
         <v>44</v>
@@ -4754,7 +4934,7 @@
       </c>
       <c r="I88" s="5"/>
       <c r="J88" s="5">
-        <v>0.1681</v>
+        <v>0.1729</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
@@ -4762,19 +4942,19 @@
         <v>6</v>
       </c>
       <c r="B89" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C89" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="D89" s="1">
         <v>3000000000</v>
       </c>
       <c r="E89" s="1">
-        <v>6513458038</v>
+        <v>7703418466</v>
       </c>
       <c r="F89" s="7">
-        <v>-1331100520</v>
+        <v>1091126833</v>
       </c>
       <c r="G89" t="s">
         <v>44</v>
@@ -4784,7 +4964,7 @@
       </c>
       <c r="I89" s="5"/>
       <c r="J89" s="5">
-        <v>0.1681</v>
+        <v>0.1729</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
@@ -4792,19 +4972,19 @@
         <v>6</v>
       </c>
       <c r="B90" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C90" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="D90" s="1">
         <v>3000000000</v>
       </c>
       <c r="E90" s="1">
-        <v>6612291633</v>
+        <v>10620801400</v>
       </c>
       <c r="F90" s="7">
-        <v>-1576257862</v>
+        <v>2435631504</v>
       </c>
       <c r="G90" t="s">
         <v>44</v>
@@ -4814,7 +4994,7 @@
       </c>
       <c r="I90" s="5"/>
       <c r="J90" s="5">
-        <v>0.1681</v>
+        <v>0.1729</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
@@ -4822,19 +5002,19 @@
         <v>6</v>
       </c>
       <c r="B91" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C91" t="s">
-        <v>43</v>
+        <v>73</v>
       </c>
       <c r="D91" s="1">
         <v>3000000000</v>
       </c>
       <c r="E91" s="1">
-        <v>8185169896</v>
+        <v>4736028698</v>
       </c>
       <c r="F91" s="7">
-        <v>-1256946817</v>
+        <v>769475644</v>
       </c>
       <c r="G91" t="s">
         <v>44</v>
@@ -4844,7 +5024,7 @@
       </c>
       <c r="I91" s="5"/>
       <c r="J91" s="5">
-        <v>0.1681</v>
+        <v>0.1729</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
@@ -4852,19 +5032,19 @@
         <v>6</v>
       </c>
       <c r="B92" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C92" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="D92" s="1">
         <v>3000000000</v>
       </c>
       <c r="E92" s="1">
-        <v>3966553054</v>
+        <v>6965496135</v>
       </c>
       <c r="F92" s="7">
-        <v>-1328383087</v>
+        <v>804730791</v>
       </c>
       <c r="G92" t="s">
         <v>44</v>
@@ -4874,27 +5054,27 @@
       </c>
       <c r="I92" s="5"/>
       <c r="J92" s="5">
-        <v>0.1681</v>
+        <v>0.1729</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B93" t="s">
         <v>88</v>
       </c>
       <c r="C93" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="D93" s="1">
-        <v>3000000000</v>
+        <v>6006437351</v>
       </c>
       <c r="E93" s="1">
-        <v>6160765344</v>
+        <v>18011209614</v>
       </c>
       <c r="F93" s="7">
-        <v>-759365736</v>
+        <v>2505150365</v>
       </c>
       <c r="G93" t="s">
         <v>44</v>
@@ -4904,7 +5084,7 @@
       </c>
       <c r="I93" s="5"/>
       <c r="J93" s="5">
-        <v>0.1681</v>
+        <v>0.17379999999999998</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
@@ -4915,16 +5095,16 @@
         <v>89</v>
       </c>
       <c r="C94" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="D94" s="1">
-        <v>6006437351</v>
+        <v>10115864773</v>
       </c>
       <c r="E94" s="1">
-        <v>15506059249</v>
+        <v>32083911327</v>
       </c>
       <c r="F94" s="7">
-        <v>-1911360124</v>
+        <v>6873510330</v>
       </c>
       <c r="G94" t="s">
         <v>44</v>
@@ -4934,7 +5114,7 @@
       </c>
       <c r="I94" s="5"/>
       <c r="J94" s="5">
-        <v>0.1689</v>
+        <v>0.127</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
@@ -4945,16 +5125,16 @@
         <v>90</v>
       </c>
       <c r="C95" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="D95" s="1">
-        <v>10115864773</v>
+        <v>1511398000</v>
       </c>
       <c r="E95" s="1">
-        <v>25210400997</v>
+        <v>4731753848</v>
       </c>
       <c r="F95" s="7">
-        <v>-3467042417</v>
+        <v>913236653</v>
       </c>
       <c r="G95" t="s">
         <v>44</v>
@@ -4964,7 +5144,7 @@
       </c>
       <c r="I95" s="5"/>
       <c r="J95" s="5">
-        <v>0.12210000000000001</v>
+        <v>0.1724</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
@@ -4972,19 +5152,19 @@
         <v>7</v>
       </c>
       <c r="B96" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C96" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D96" s="1">
-        <v>1511398000</v>
+        <v>2849479862</v>
       </c>
       <c r="E96" s="1">
-        <v>3818517195</v>
+        <v>7951381718</v>
       </c>
       <c r="F96" s="7">
-        <v>-808647247</v>
+        <v>997168146</v>
       </c>
       <c r="G96" t="s">
         <v>44</v>
@@ -4994,7 +5174,7 @@
       </c>
       <c r="I96" s="5"/>
       <c r="J96" s="5">
-        <v>0.1675</v>
+        <v>0.1724</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
@@ -5002,19 +5182,19 @@
         <v>7</v>
       </c>
       <c r="B97" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C97" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="D97" s="1">
-        <v>2849479862</v>
+        <v>1370065623</v>
       </c>
       <c r="E97" s="1">
-        <v>6954213572</v>
+        <v>4132185673</v>
       </c>
       <c r="F97" s="7">
-        <v>-1093007069</v>
+        <v>528877218</v>
       </c>
       <c r="G97" t="s">
         <v>44</v>
@@ -5024,7 +5204,7 @@
       </c>
       <c r="I97" s="5"/>
       <c r="J97" s="5">
-        <v>0.1675</v>
+        <v>0.1724</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
@@ -5032,19 +5212,19 @@
         <v>7</v>
       </c>
       <c r="B98" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C98" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D98" s="1">
-        <v>1370065623</v>
+        <v>1045683565</v>
       </c>
       <c r="E98" s="1">
-        <v>3603308455</v>
+        <v>2824007160</v>
       </c>
       <c r="F98" s="7">
-        <v>-432746327</v>
+        <v>355606257</v>
       </c>
       <c r="G98" t="s">
         <v>44</v>
@@ -5054,7 +5234,7 @@
       </c>
       <c r="I98" s="5"/>
       <c r="J98" s="5">
-        <v>0.1675</v>
+        <v>0.1724</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
@@ -5062,19 +5242,19 @@
         <v>7</v>
       </c>
       <c r="B99" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C99" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="D99" s="1">
-        <v>1045683565</v>
+        <v>1478582277</v>
       </c>
       <c r="E99" s="1">
-        <v>2468400903</v>
+        <v>3135946856</v>
       </c>
       <c r="F99" s="7">
-        <v>-433264662</v>
+        <v>343033498</v>
       </c>
       <c r="G99" t="s">
         <v>44</v>
@@ -5084,7 +5264,7 @@
       </c>
       <c r="I99" s="5"/>
       <c r="J99" s="5">
-        <v>0.1675</v>
+        <v>0.1724</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
@@ -5092,19 +5272,19 @@
         <v>7</v>
       </c>
       <c r="B100" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C100" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D100" s="1">
-        <v>1478582277</v>
+        <v>1492252844</v>
       </c>
       <c r="E100" s="1">
-        <v>2792913358</v>
+        <v>3923692246</v>
       </c>
       <c r="F100" s="7">
-        <v>-467485995</v>
+        <v>468723788</v>
       </c>
       <c r="G100" t="s">
         <v>44</v>
@@ -5114,57 +5294,55 @@
       </c>
       <c r="I100" s="5"/>
       <c r="J100" s="5">
-        <v>0.1675</v>
+        <v>0.1724</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B101" t="s">
         <v>91</v>
       </c>
       <c r="C101" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D101" s="1">
-        <v>1492252844</v>
+        <v>0</v>
       </c>
       <c r="E101" s="1">
-        <v>3454968458</v>
+        <v>0</v>
       </c>
       <c r="F101" s="7">
-        <v>-387037767</v>
+        <v>-2330215349</v>
       </c>
       <c r="G101" t="s">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="H101" t="s">
         <v>45</v>
       </c>
       <c r="I101" s="5"/>
-      <c r="J101" s="5">
-        <v>0.1675</v>
-      </c>
+      <c r="J101" s="5"/>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B102" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="C102" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="D102" s="1">
-        <v>500000000</v>
+        <v>0</v>
       </c>
       <c r="E102" s="1">
-        <v>1165423958</v>
+        <v>0</v>
       </c>
       <c r="F102" s="7">
-        <v>1165423958</v>
+        <v>-2302140221</v>
       </c>
       <c r="G102" t="s">
         <v>92</v>
@@ -5173,28 +5351,26 @@
         <v>45</v>
       </c>
       <c r="I102" s="5"/>
-      <c r="J102" s="5">
-        <v>1.2554</v>
-      </c>
+      <c r="J102" s="5"/>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B103" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="C103" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D103" s="1">
-        <v>500000000</v>
+        <v>0</v>
       </c>
       <c r="E103" s="1">
-        <v>1151125436</v>
+        <v>0</v>
       </c>
       <c r="F103" s="7">
-        <v>1151125436</v>
+        <v>-2297488877</v>
       </c>
       <c r="G103" t="s">
         <v>92</v>
@@ -5203,28 +5379,26 @@
         <v>45</v>
       </c>
       <c r="I103" s="5"/>
-      <c r="J103" s="5">
-        <v>1.2554</v>
-      </c>
+      <c r="J103" s="5"/>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B104" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="C104" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D104" s="1">
-        <v>500000000</v>
+        <v>0</v>
       </c>
       <c r="E104" s="1">
-        <v>1148829895</v>
+        <v>0</v>
       </c>
       <c r="F104" s="7">
-        <v>1148829895</v>
+        <v>-2374031106</v>
       </c>
       <c r="G104" t="s">
         <v>92</v>
@@ -5233,28 +5407,26 @@
         <v>45</v>
       </c>
       <c r="I104" s="5"/>
-      <c r="J104" s="5">
-        <v>1.2554</v>
-      </c>
+      <c r="J104" s="5"/>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B105" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="C105" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="D105" s="1">
-        <v>500000000</v>
+        <v>0</v>
       </c>
       <c r="E105" s="1">
-        <v>1186966069</v>
+        <v>0</v>
       </c>
       <c r="F105" s="7">
-        <v>1186966069</v>
+        <v>-2293703108</v>
       </c>
       <c r="G105" t="s">
         <v>92</v>
@@ -5263,169 +5435,157 @@
         <v>45</v>
       </c>
       <c r="I105" s="5"/>
-      <c r="J105" s="5">
-        <v>1.2554</v>
-      </c>
+      <c r="J105" s="5"/>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B106" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C106" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D106" s="1">
-        <v>3000000000</v>
+        <v>0</v>
       </c>
       <c r="E106" s="1">
-        <v>3958912304</v>
+        <v>0</v>
       </c>
       <c r="F106" s="7">
-        <v>1380163332</v>
+        <v>-1165423958</v>
       </c>
       <c r="G106" t="s">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="H106" t="s">
         <v>45</v>
       </c>
       <c r="I106" s="5"/>
-      <c r="J106" s="5">
-        <v>1.1673</v>
-      </c>
+      <c r="J106" s="5"/>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B107" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C107" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D107" s="1">
-        <v>3000000000</v>
+        <v>0</v>
       </c>
       <c r="E107" s="1">
-        <v>3975895368</v>
+        <v>0</v>
       </c>
       <c r="F107" s="7">
-        <v>1397858568</v>
+        <v>-1151125436</v>
       </c>
       <c r="G107" t="s">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="H107" t="s">
         <v>45</v>
       </c>
       <c r="I107" s="5"/>
-      <c r="J107" s="5">
-        <v>1.1673</v>
-      </c>
+      <c r="J107" s="5"/>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B108" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="C108" t="s">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="D108" s="1">
-        <v>400000000</v>
+        <v>0</v>
       </c>
       <c r="E108" s="1">
-        <v>381187393</v>
+        <v>0</v>
       </c>
       <c r="F108" s="7">
-        <v>-30591888</v>
+        <v>-1148829895</v>
       </c>
       <c r="G108" t="s">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="H108" t="s">
         <v>45</v>
       </c>
       <c r="I108" s="5"/>
-      <c r="J108" s="5">
-        <v>0.009000000000000001</v>
-      </c>
+      <c r="J108" s="5"/>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B109" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="C109" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="D109" s="1">
-        <v>400000000</v>
+        <v>0</v>
       </c>
       <c r="E109" s="1">
-        <v>333326095</v>
+        <v>0</v>
       </c>
       <c r="F109" s="7">
-        <v>-59815011</v>
+        <v>-1186966069</v>
       </c>
       <c r="G109" t="s">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="H109" t="s">
         <v>45</v>
       </c>
       <c r="I109" s="5"/>
-      <c r="J109" s="5">
-        <v>0.009000000000000001</v>
-      </c>
+      <c r="J109" s="5"/>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>8</v>
       </c>
       <c r="B110" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C110" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="D110" s="1">
-        <v>400000000</v>
+        <v>0</v>
       </c>
       <c r="E110" s="1">
-        <v>341538111</v>
+        <v>0</v>
       </c>
       <c r="F110" s="7">
-        <v>-55332604</v>
+        <v>-3958912304</v>
       </c>
       <c r="G110" t="s">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="H110" t="s">
         <v>45</v>
       </c>
       <c r="I110" s="5"/>
-      <c r="J110" s="5">
-        <v>0.009000000000000001</v>
-      </c>
+      <c r="J110" s="5"/>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B111" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C111" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="D111" s="1">
         <v>0</v>
@@ -5434,10 +5594,10 @@
         <v>0</v>
       </c>
       <c r="F111" s="7">
-        <v>-1528889549</v>
+        <v>-3975895368</v>
       </c>
       <c r="G111" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H111" t="s">
         <v>45</v>
@@ -5447,13 +5607,13 @@
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B112" t="s">
         <v>80</v>
       </c>
       <c r="C112" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="D112" s="1">
         <v>0</v>
@@ -5462,10 +5622,10 @@
         <v>0</v>
       </c>
       <c r="F112" s="7">
-        <v>-1474347055</v>
+        <v>-381187393</v>
       </c>
       <c r="G112" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H112" t="s">
         <v>45</v>
@@ -5475,13 +5635,13 @@
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B113" t="s">
         <v>80</v>
       </c>
       <c r="C113" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="D113" s="1">
         <v>0</v>
@@ -5490,10 +5650,10 @@
         <v>0</v>
       </c>
       <c r="F113" s="7">
-        <v>-1489331693</v>
+        <v>-333326095</v>
       </c>
       <c r="G113" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H113" t="s">
         <v>45</v>
@@ -5503,13 +5663,13 @@
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B114" t="s">
         <v>80</v>
       </c>
       <c r="C114" t="s">
-        <v>77</v>
+        <v>43</v>
       </c>
       <c r="D114" s="1">
         <v>0</v>
@@ -5518,10 +5678,10 @@
         <v>0</v>
       </c>
       <c r="F114" s="7">
-        <v>-1492945981</v>
+        <v>-341538111</v>
       </c>
       <c r="G114" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H114" t="s">
         <v>45</v>
@@ -5537,7 +5697,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J186"/>
+  <dimension ref="A1:J190"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="22" customWidth="1"/>
@@ -5584,29 +5744,29 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C2" t="s">
         <v>94</v>
-      </c>
-      <c r="C2" t="s">
-        <v>95</v>
       </c>
       <c r="D2" s="1">
         <v>900495639</v>
       </c>
       <c r="E2" s="1">
-        <v>897752897</v>
+        <v>901079345</v>
       </c>
       <c r="F2" s="7">
-        <v>-6520966</v>
+        <v>901079345</v>
       </c>
       <c r="G2" t="s">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="H2" t="s">
         <v>96</v>
       </c>
       <c r="I2" s="5"/>
       <c r="J2" s="5">
-        <v>-0.0048</v>
+        <v>-0.0005</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -5614,7 +5774,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C3" t="s">
         <v>97</v>
@@ -5623,20 +5783,20 @@
         <v>1338657958</v>
       </c>
       <c r="E3" s="1">
-        <v>1334569313</v>
+        <v>1340532856</v>
       </c>
       <c r="F3" s="7">
-        <v>-7251097</v>
+        <v>1340532856</v>
       </c>
       <c r="G3" t="s">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="H3" t="s">
         <v>96</v>
       </c>
       <c r="I3" s="5"/>
       <c r="J3" s="5">
-        <v>-0.0048</v>
+        <v>-0.0005</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -5650,13 +5810,13 @@
         <v>99</v>
       </c>
       <c r="D4" s="1">
-        <v>2408967886</v>
+        <v>2558967886</v>
       </c>
       <c r="E4" s="1">
-        <v>2364612047</v>
+        <v>2526946832</v>
       </c>
       <c r="F4" s="7">
-        <v>-22907566</v>
+        <v>162334785</v>
       </c>
       <c r="G4" t="s">
         <v>44</v>
@@ -5666,7 +5826,7 @@
       </c>
       <c r="I4" s="5"/>
       <c r="J4" s="5">
-        <v>-0.07490000000000001</v>
+        <v>-0.0709</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -5683,10 +5843,10 @@
         <v>2034805538</v>
       </c>
       <c r="E5" s="1">
-        <v>3608745347</v>
+        <v>3696336168</v>
       </c>
       <c r="F5" s="7">
-        <v>232055969</v>
+        <v>87590821</v>
       </c>
       <c r="G5" t="s">
         <v>44</v>
@@ -5696,7 +5856,7 @@
       </c>
       <c r="I5" s="5"/>
       <c r="J5" s="5">
-        <v>0.6754000000000001</v>
+        <v>0.7202</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -5713,10 +5873,10 @@
         <v>1585120883</v>
       </c>
       <c r="E6" s="1">
-        <v>2656287171</v>
+        <v>2716470918</v>
       </c>
       <c r="F6" s="7">
-        <v>6278013</v>
+        <v>60183747</v>
       </c>
       <c r="G6" t="s">
         <v>44</v>
@@ -5726,7 +5886,7 @@
       </c>
       <c r="I6" s="5"/>
       <c r="J6" s="5">
-        <v>0.6754000000000001</v>
+        <v>0.7202</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -5743,20 +5903,20 @@
         <v>656507639</v>
       </c>
       <c r="E7" s="1">
-        <v>1304933202</v>
+        <v>1336860928</v>
       </c>
       <c r="F7" s="7">
-        <v>11196846</v>
+        <v>1336860928</v>
       </c>
       <c r="G7" t="s">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="H7" t="s">
         <v>96</v>
       </c>
       <c r="I7" s="5"/>
       <c r="J7" s="5">
-        <v>0.882</v>
+        <v>0.9419</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -5773,10 +5933,10 @@
         <v>1321092316</v>
       </c>
       <c r="E8" s="1">
-        <v>2348868079</v>
+        <v>2414233497</v>
       </c>
       <c r="F8" s="7">
-        <v>-5498903</v>
+        <v>65365418</v>
       </c>
       <c r="G8" t="s">
         <v>44</v>
@@ -5786,7 +5946,7 @@
       </c>
       <c r="I8" s="5"/>
       <c r="J8" s="5">
-        <v>0.8704999999999999</v>
+        <v>0.9205</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -5803,10 +5963,10 @@
         <v>1783655177</v>
       </c>
       <c r="E9" s="1">
-        <v>3175972208</v>
+        <v>3256489722</v>
       </c>
       <c r="F9" s="7">
-        <v>6605173</v>
+        <v>80517514</v>
       </c>
       <c r="G9" t="s">
         <v>44</v>
@@ -5816,7 +5976,7 @@
       </c>
       <c r="I9" s="5"/>
       <c r="J9" s="5">
-        <v>0.8704999999999999</v>
+        <v>0.9205</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -5833,20 +5993,20 @@
         <v>1683240295</v>
       </c>
       <c r="E10" s="1">
-        <v>1714089252</v>
+        <v>1752353167</v>
       </c>
       <c r="F10" s="7">
-        <v>1714089252</v>
+        <v>1752353167</v>
       </c>
       <c r="G10" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="H10" t="s">
         <v>96</v>
       </c>
       <c r="I10" s="5"/>
       <c r="J10" s="5">
-        <v>0.0174</v>
+        <v>0.0418</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -5863,20 +6023,20 @@
         <v>1687228552</v>
       </c>
       <c r="E11" s="1">
-        <v>1711777799</v>
+        <v>1751287343</v>
       </c>
       <c r="F11" s="7">
-        <v>1711777799</v>
+        <v>1751287343</v>
       </c>
       <c r="G11" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="H11" t="s">
         <v>96</v>
       </c>
       <c r="I11" s="5"/>
       <c r="J11" s="5">
-        <v>0.0174</v>
+        <v>0.0418</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
@@ -5893,10 +6053,10 @@
         <v>2555932432</v>
       </c>
       <c r="E12" s="1">
-        <v>2941839542</v>
+        <v>2848023524</v>
       </c>
       <c r="F12" s="7">
-        <v>79438726</v>
+        <v>-93816018</v>
       </c>
       <c r="G12" t="s">
         <v>44</v>
@@ -5921,10 +6081,10 @@
         <v>1417127452</v>
       </c>
       <c r="E13" s="1">
-        <v>1552479450</v>
+        <v>1507978389</v>
       </c>
       <c r="F13" s="7">
-        <v>43035694</v>
+        <v>-44501061</v>
       </c>
       <c r="G13" t="s">
         <v>44</v>
@@ -5949,20 +6109,20 @@
         <v>618843493</v>
       </c>
       <c r="E14" s="1">
-        <v>769778438</v>
+        <v>775171961</v>
       </c>
       <c r="F14" s="7">
-        <v>-7734260</v>
+        <v>775171961</v>
       </c>
       <c r="G14" t="s">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="H14" t="s">
         <v>96</v>
       </c>
       <c r="I14" s="5"/>
       <c r="J14" s="5">
-        <v>0.2728</v>
+        <v>0.2836</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -5979,20 +6139,20 @@
         <v>1263392347</v>
       </c>
       <c r="E15" s="1">
-        <v>1666508211</v>
+        <v>1712693938</v>
       </c>
       <c r="F15" s="7">
-        <v>45958505</v>
+        <v>1712693938</v>
       </c>
       <c r="G15" t="s">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="H15" t="s">
         <v>96</v>
       </c>
       <c r="I15" s="5"/>
       <c r="J15" s="5">
-        <v>0.3337</v>
+        <v>0.3711</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -6009,20 +6169,20 @@
         <v>1352011599</v>
       </c>
       <c r="E16" s="1">
-        <v>1781352129</v>
+        <v>1830792196</v>
       </c>
       <c r="F16" s="7">
-        <v>49415079</v>
+        <v>1830792196</v>
       </c>
       <c r="G16" t="s">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="H16" t="s">
         <v>96</v>
       </c>
       <c r="I16" s="5"/>
       <c r="J16" s="5">
-        <v>0.3337</v>
+        <v>0.3711</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
@@ -6039,10 +6199,10 @@
         <v>1796000834</v>
       </c>
       <c r="E17" s="1">
-        <v>2098200969</v>
+        <v>2067584920</v>
       </c>
       <c r="F17" s="7">
-        <v>-4941952</v>
+        <v>-30616049</v>
       </c>
       <c r="G17" t="s">
         <v>44</v>
@@ -6052,7 +6212,7 @@
       </c>
       <c r="I17" s="5"/>
       <c r="J17" s="5">
-        <v>0.5083</v>
+        <v>0.5336</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
@@ -6069,10 +6229,10 @@
         <v>1164480846</v>
       </c>
       <c r="E18" s="1">
-        <v>1785160367</v>
+        <v>1797726702</v>
       </c>
       <c r="F18" s="7">
-        <v>66873759</v>
+        <v>12566335</v>
       </c>
       <c r="G18" t="s">
         <v>44</v>
@@ -6082,7 +6242,7 @@
       </c>
       <c r="I18" s="5"/>
       <c r="J18" s="5">
-        <v>0.5083</v>
+        <v>0.5336</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -6099,10 +6259,10 @@
         <v>1507914919</v>
       </c>
       <c r="E19" s="1">
-        <v>2290978822</v>
+        <v>2310037806</v>
       </c>
       <c r="F19" s="7">
-        <v>76464879</v>
+        <v>19058984</v>
       </c>
       <c r="G19" t="s">
         <v>44</v>
@@ -6112,7 +6272,7 @@
       </c>
       <c r="I19" s="5"/>
       <c r="J19" s="5">
-        <v>0.5083</v>
+        <v>0.5336</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -6129,20 +6289,20 @@
         <v>1186559371</v>
       </c>
       <c r="E20" s="1">
-        <v>1352096519</v>
+        <v>1359557078</v>
       </c>
       <c r="F20" s="7">
-        <v>-15992016</v>
+        <v>1359557078</v>
       </c>
       <c r="G20" t="s">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="H20" t="s">
         <v>96</v>
       </c>
       <c r="I20" s="5"/>
       <c r="J20" s="5">
-        <v>0.1376</v>
+        <v>0.14400000000000002</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -6159,20 +6319,20 @@
         <v>670392768</v>
       </c>
       <c r="E21" s="1">
-        <v>760653316</v>
+        <v>764677694</v>
       </c>
       <c r="F21" s="7">
-        <v>-8033409</v>
+        <v>764677694</v>
       </c>
       <c r="G21" t="s">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="H21" t="s">
         <v>96</v>
       </c>
       <c r="I21" s="5"/>
       <c r="J21" s="5">
-        <v>0.1376</v>
+        <v>0.14400000000000002</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -6189,20 +6349,20 @@
         <v>941561542</v>
       </c>
       <c r="E22" s="1">
-        <v>1065528056</v>
+        <v>1071245991</v>
       </c>
       <c r="F22" s="7">
-        <v>-12213749</v>
+        <v>1071245991</v>
       </c>
       <c r="G22" t="s">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="H22" t="s">
         <v>96</v>
       </c>
       <c r="I22" s="5"/>
       <c r="J22" s="5">
-        <v>0.1376</v>
+        <v>0.14400000000000002</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -6219,10 +6379,10 @@
         <v>3222313413</v>
       </c>
       <c r="E23" s="1">
-        <v>3904111203</v>
+        <v>3997930675</v>
       </c>
       <c r="F23" s="7">
-        <v>-71469561</v>
+        <v>93819472</v>
       </c>
       <c r="G23" t="s">
         <v>44</v>
@@ -6232,7 +6392,7 @@
       </c>
       <c r="I23" s="5"/>
       <c r="J23" s="5">
-        <v>0.21989999999999998</v>
+        <v>0.2486</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -6249,20 +6409,20 @@
         <v>3208355339</v>
       </c>
       <c r="E24" s="1">
-        <v>3866001108</v>
+        <v>3955468695</v>
       </c>
       <c r="F24" s="7">
-        <v>3866001108</v>
+        <v>89467587</v>
       </c>
       <c r="G24" t="s">
-        <v>92</v>
+        <v>44</v>
       </c>
       <c r="H24" t="s">
         <v>96</v>
       </c>
       <c r="I24" s="5"/>
       <c r="J24" s="5">
-        <v>0.21989999999999998</v>
+        <v>0.2486</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -6279,10 +6439,10 @@
         <v>3189006741</v>
       </c>
       <c r="E25" s="1">
-        <v>3853735625</v>
+        <v>3946610359</v>
       </c>
       <c r="F25" s="7">
-        <v>-68827965</v>
+        <v>92874734</v>
       </c>
       <c r="G25" t="s">
         <v>44</v>
@@ -6292,7 +6452,7 @@
       </c>
       <c r="I25" s="5"/>
       <c r="J25" s="5">
-        <v>0.21989999999999998</v>
+        <v>0.2486</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -6309,20 +6469,20 @@
         <v>1159305130</v>
       </c>
       <c r="E26" s="1">
-        <v>1318692011</v>
+        <v>1293678966</v>
       </c>
       <c r="F26" s="7">
-        <v>1318692011</v>
+        <v>-25013045</v>
       </c>
       <c r="G26" t="s">
-        <v>92</v>
+        <v>44</v>
       </c>
       <c r="H26" t="s">
         <v>96</v>
       </c>
       <c r="I26" s="5"/>
       <c r="J26" s="5">
-        <v>0.1247</v>
+        <v>0.10369999999999999</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
@@ -6339,20 +6499,20 @@
         <v>1668471152</v>
       </c>
       <c r="E27" s="1">
-        <v>1836404740</v>
+        <v>1797336875</v>
       </c>
       <c r="F27" s="7">
-        <v>1836404740</v>
+        <v>-39067865</v>
       </c>
       <c r="G27" t="s">
-        <v>92</v>
+        <v>44</v>
       </c>
       <c r="H27" t="s">
         <v>96</v>
       </c>
       <c r="I27" s="5"/>
       <c r="J27" s="5">
-        <v>0.1247</v>
+        <v>0.10369999999999999</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -6366,23 +6526,23 @@
         <v>79</v>
       </c>
       <c r="D28" s="1">
-        <v>949175052</v>
+        <v>1707512798</v>
       </c>
       <c r="E28" s="1">
-        <v>1656860388</v>
+        <v>1715405818</v>
       </c>
       <c r="F28" s="7">
-        <v>-61990147</v>
+        <v>1715405818</v>
       </c>
       <c r="G28" t="s">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="H28" t="s">
         <v>96</v>
       </c>
       <c r="I28" s="5"/>
       <c r="J28" s="5">
-        <v>0.6866</v>
+        <v>0.0045000000000000005</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -6399,10 +6559,10 @@
         <v>641552002</v>
       </c>
       <c r="E29" s="1">
-        <v>1179392915</v>
+        <v>1220326622</v>
       </c>
       <c r="F29" s="7">
-        <v>-5865687</v>
+        <v>40933707</v>
       </c>
       <c r="G29" t="s">
         <v>44</v>
@@ -6412,7 +6572,7 @@
       </c>
       <c r="I29" s="5"/>
       <c r="J29" s="5">
-        <v>0.914</v>
+        <v>0.9765</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -6429,10 +6589,10 @@
         <v>848715051</v>
       </c>
       <c r="E30" s="1">
-        <v>1520309377</v>
+        <v>1567126369</v>
       </c>
       <c r="F30" s="7">
-        <v>-1531838</v>
+        <v>46816992</v>
       </c>
       <c r="G30" t="s">
         <v>44</v>
@@ -6442,7 +6602,7 @@
       </c>
       <c r="I30" s="5"/>
       <c r="J30" s="5">
-        <v>0.914</v>
+        <v>0.9765</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -6459,10 +6619,10 @@
         <v>849045562</v>
       </c>
       <c r="E31" s="1">
-        <v>1538613293</v>
+        <v>1587306347</v>
       </c>
       <c r="F31" s="7">
-        <v>-2206522</v>
+        <v>48693054</v>
       </c>
       <c r="G31" t="s">
         <v>44</v>
@@ -6472,7 +6632,7 @@
       </c>
       <c r="I31" s="5"/>
       <c r="J31" s="5">
-        <v>0.914</v>
+        <v>0.9765</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -6489,10 +6649,10 @@
         <v>762047560</v>
       </c>
       <c r="E32" s="1">
-        <v>1408516487</v>
+        <v>1452471596</v>
       </c>
       <c r="F32" s="7">
-        <v>-3741370</v>
+        <v>43955109</v>
       </c>
       <c r="G32" t="s">
         <v>44</v>
@@ -6502,7 +6662,7 @@
       </c>
       <c r="I32" s="5"/>
       <c r="J32" s="5">
-        <v>0.914</v>
+        <v>0.9765</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -6519,10 +6679,10 @@
         <v>427360620</v>
       </c>
       <c r="E33" s="1">
-        <v>523380643</v>
+        <v>525529138</v>
       </c>
       <c r="F33" s="7">
-        <v>502276</v>
+        <v>2148495</v>
       </c>
       <c r="G33" t="s">
         <v>44</v>
@@ -6547,10 +6707,10 @@
         <v>905211657</v>
       </c>
       <c r="E34" s="1">
-        <v>1164994046</v>
+        <v>1168816199</v>
       </c>
       <c r="F34" s="7">
-        <v>2212877</v>
+        <v>3822153</v>
       </c>
       <c r="G34" t="s">
         <v>44</v>
@@ -6575,10 +6735,10 @@
         <v>1039618153</v>
       </c>
       <c r="E35" s="1">
-        <v>1287714646</v>
+        <v>1292125290</v>
       </c>
       <c r="F35" s="7">
-        <v>-360968</v>
+        <v>4410644</v>
       </c>
       <c r="G35" t="s">
         <v>44</v>
@@ -6603,10 +6763,10 @@
         <v>1006698949</v>
       </c>
       <c r="E36" s="1">
-        <v>1523316004</v>
+        <v>1535900143</v>
       </c>
       <c r="F36" s="7">
-        <v>24254831</v>
+        <v>12584139</v>
       </c>
       <c r="G36" t="s">
         <v>44</v>
@@ -6616,7 +6776,7 @@
       </c>
       <c r="I36" s="5"/>
       <c r="J36" s="5">
-        <v>0.4412</v>
+        <v>0.4625</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -6633,10 +6793,10 @@
         <v>867219463</v>
       </c>
       <c r="E37" s="1">
-        <v>1147513598</v>
+        <v>1159978150</v>
       </c>
       <c r="F37" s="7">
-        <v>9050732</v>
+        <v>12464552</v>
       </c>
       <c r="G37" t="s">
         <v>44</v>
@@ -6646,7 +6806,7 @@
       </c>
       <c r="I37" s="5"/>
       <c r="J37" s="5">
-        <v>0.4412</v>
+        <v>0.4625</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -6663,10 +6823,10 @@
         <v>938885217</v>
       </c>
       <c r="E38" s="1">
-        <v>1316573361</v>
+        <v>1354927450</v>
       </c>
       <c r="F38" s="7">
-        <v>10162178</v>
+        <v>38354089</v>
       </c>
       <c r="G38" t="s">
         <v>44</v>
@@ -6676,7 +6836,7 @@
       </c>
       <c r="I38" s="5"/>
       <c r="J38" s="5">
-        <v>0.4412</v>
+        <v>0.4625</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
@@ -6693,10 +6853,10 @@
         <v>806462703</v>
       </c>
       <c r="E39" s="1">
-        <v>1142750317</v>
+        <v>1156758978</v>
       </c>
       <c r="F39" s="7">
-        <v>-536251384</v>
+        <v>-607971276</v>
       </c>
       <c r="G39" t="s">
         <v>44</v>
@@ -6706,7 +6866,7 @@
       </c>
       <c r="I39" s="5"/>
       <c r="J39" s="5">
-        <v>0.4412</v>
+        <v>0.4625</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
@@ -6723,10 +6883,10 @@
         <v>559865985</v>
       </c>
       <c r="E40" s="1">
-        <v>792418771</v>
+        <v>795687952</v>
       </c>
       <c r="F40" s="7">
-        <v>37354910</v>
+        <v>3269181</v>
       </c>
       <c r="G40" t="s">
         <v>44</v>
@@ -6736,7 +6896,7 @@
       </c>
       <c r="I40" s="5"/>
       <c r="J40" s="5">
-        <v>0.4412</v>
+        <v>0.4625</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
@@ -6753,10 +6913,10 @@
         <v>506416368</v>
       </c>
       <c r="E41" s="1">
-        <v>697308846</v>
+        <v>706823715</v>
       </c>
       <c r="F41" s="7">
-        <v>31087972</v>
+        <v>9514869</v>
       </c>
       <c r="G41" t="s">
         <v>44</v>
@@ -6766,7 +6926,7 @@
       </c>
       <c r="I41" s="5"/>
       <c r="J41" s="5">
-        <v>0.4412</v>
+        <v>0.4625</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -6783,10 +6943,10 @@
         <v>441937598</v>
       </c>
       <c r="E42" s="1">
-        <v>621979937</v>
+        <v>625971021</v>
       </c>
       <c r="F42" s="7">
-        <v>-1057021764</v>
+        <v>-1138759233</v>
       </c>
       <c r="G42" t="s">
         <v>44</v>
@@ -6796,7 +6956,7 @@
       </c>
       <c r="I42" s="5"/>
       <c r="J42" s="5">
-        <v>0.4412</v>
+        <v>0.4625</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
@@ -6813,10 +6973,10 @@
         <v>1059063706</v>
       </c>
       <c r="E43" s="1">
-        <v>1049063723</v>
+        <v>1053509055</v>
       </c>
       <c r="F43" s="7">
-        <v>-17082600</v>
+        <v>4445332</v>
       </c>
       <c r="G43" t="s">
         <v>44</v>
@@ -6826,7 +6986,7 @@
       </c>
       <c r="I43" s="5"/>
       <c r="J43" s="5">
-        <v>-0.0070999999999999995</v>
+        <v>-0.003</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
@@ -6843,10 +7003,10 @@
         <v>558802476</v>
       </c>
       <c r="E44" s="1">
-        <v>554364692</v>
+        <v>556587232</v>
       </c>
       <c r="F44" s="7">
-        <v>-8893677</v>
+        <v>2222540</v>
       </c>
       <c r="G44" t="s">
         <v>44</v>
@@ -6856,7 +7016,7 @@
       </c>
       <c r="I44" s="5"/>
       <c r="J44" s="5">
-        <v>-0.0070999999999999995</v>
+        <v>-0.003</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
@@ -6873,10 +7033,10 @@
         <v>674765647</v>
       </c>
       <c r="E45" s="1">
-        <v>668540853</v>
+        <v>670818582</v>
       </c>
       <c r="F45" s="7">
-        <v>-10700769</v>
+        <v>2277729</v>
       </c>
       <c r="G45" t="s">
         <v>44</v>
@@ -6886,7 +7046,7 @@
       </c>
       <c r="I45" s="5"/>
       <c r="J45" s="5">
-        <v>-0.0070999999999999995</v>
+        <v>-0.003</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
@@ -6903,10 +7063,10 @@
         <v>430000000</v>
       </c>
       <c r="E46" s="1">
-        <v>578472486</v>
+        <v>569783360</v>
       </c>
       <c r="F46" s="7">
-        <v>-1988798</v>
+        <v>-8689126</v>
       </c>
       <c r="G46" t="s">
         <v>44</v>
@@ -6916,7 +7076,7 @@
       </c>
       <c r="I46" s="5"/>
       <c r="J46" s="5">
-        <v>0.39909999999999995</v>
+        <v>0.3736</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
@@ -6933,10 +7093,10 @@
         <v>700000000</v>
       </c>
       <c r="E47" s="1">
-        <v>957679882</v>
+        <v>943529926</v>
       </c>
       <c r="F47" s="7">
-        <v>-1809574</v>
+        <v>-14149956</v>
       </c>
       <c r="G47" t="s">
         <v>44</v>
@@ -6946,7 +7106,7 @@
       </c>
       <c r="I47" s="5"/>
       <c r="J47" s="5">
-        <v>0.39909999999999995</v>
+        <v>0.3736</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
@@ -6963,10 +7123,10 @@
         <v>350000000</v>
       </c>
       <c r="E48" s="1">
-        <v>487745804</v>
+        <v>475922222</v>
       </c>
       <c r="F48" s="7">
-        <v>-5749257</v>
+        <v>-11823582</v>
       </c>
       <c r="G48" t="s">
         <v>44</v>
@@ -6976,7 +7136,7 @@
       </c>
       <c r="I48" s="5"/>
       <c r="J48" s="5">
-        <v>0.39909999999999995</v>
+        <v>0.3736</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
@@ -6993,10 +7153,10 @@
         <v>430000000</v>
       </c>
       <c r="E49" s="1">
-        <v>583830731</v>
+        <v>574043538</v>
       </c>
       <c r="F49" s="7">
-        <v>6753960</v>
+        <v>-9787193</v>
       </c>
       <c r="G49" t="s">
         <v>44</v>
@@ -7006,7 +7166,7 @@
       </c>
       <c r="I49" s="5"/>
       <c r="J49" s="5">
-        <v>0.39909999999999995</v>
+        <v>0.3736</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
@@ -7023,10 +7183,10 @@
         <v>400000000</v>
       </c>
       <c r="E50" s="1">
-        <v>515794235</v>
+        <v>526718108</v>
       </c>
       <c r="F50" s="7">
-        <v>-15067728</v>
+        <v>10923873</v>
       </c>
       <c r="G50" t="s">
         <v>44</v>
@@ -7051,10 +7211,10 @@
         <v>400000000</v>
       </c>
       <c r="E51" s="1">
-        <v>487389833</v>
+        <v>498259486</v>
       </c>
       <c r="F51" s="7">
-        <v>-3435319</v>
+        <v>10869653</v>
       </c>
       <c r="G51" t="s">
         <v>44</v>
@@ -7079,10 +7239,10 @@
         <v>400000000</v>
       </c>
       <c r="E52" s="1">
-        <v>491940624</v>
+        <v>502875307</v>
       </c>
       <c r="F52" s="7">
-        <v>533187</v>
+        <v>10934683</v>
       </c>
       <c r="G52" t="s">
         <v>44</v>
@@ -7107,10 +7267,10 @@
         <v>400000000</v>
       </c>
       <c r="E53" s="1">
-        <v>538651033</v>
+        <v>547910625</v>
       </c>
       <c r="F53" s="7">
-        <v>-97334</v>
+        <v>9259592</v>
       </c>
       <c r="G53" t="s">
         <v>44</v>
@@ -7135,10 +7295,10 @@
         <v>400000000</v>
       </c>
       <c r="E54" s="1">
-        <v>509014558</v>
+        <v>522845162</v>
       </c>
       <c r="F54" s="7">
-        <v>-3371138</v>
+        <v>13830604</v>
       </c>
       <c r="G54" t="s">
         <v>44</v>
@@ -7163,10 +7323,10 @@
         <v>400000000</v>
       </c>
       <c r="E55" s="1">
-        <v>617340295</v>
+        <v>632835390</v>
       </c>
       <c r="F55" s="7">
-        <v>-8554071</v>
+        <v>15495095</v>
       </c>
       <c r="G55" t="s">
         <v>44</v>
@@ -7185,19 +7345,19 @@
         <v>146</v>
       </c>
       <c r="C56" t="s">
-        <v>147</v>
+        <v>121</v>
       </c>
       <c r="D56" s="1">
         <v>400000000</v>
       </c>
       <c r="E56" s="1">
-        <v>593041556</v>
+        <v>612888370</v>
       </c>
       <c r="F56" s="7">
-        <v>-6506126</v>
+        <v>612888370</v>
       </c>
       <c r="G56" t="s">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="H56" t="s">
         <v>96</v>
@@ -7213,16 +7373,16 @@
         <v>146</v>
       </c>
       <c r="C57" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D57" s="1">
         <v>400000000</v>
       </c>
       <c r="E57" s="1">
-        <v>603262281</v>
+        <v>618383558</v>
       </c>
       <c r="F57" s="7">
-        <v>-3239957</v>
+        <v>15121277</v>
       </c>
       <c r="G57" t="s">
         <v>44</v>
@@ -7247,10 +7407,10 @@
         <v>400000000</v>
       </c>
       <c r="E58" s="1">
-        <v>580538915</v>
+        <v>598887884</v>
       </c>
       <c r="F58" s="7">
-        <v>1682150</v>
+        <v>18348969</v>
       </c>
       <c r="G58" t="s">
         <v>44</v>
@@ -7275,10 +7435,10 @@
         <v>400000000</v>
       </c>
       <c r="E59" s="1">
-        <v>616317921</v>
+        <v>633942676</v>
       </c>
       <c r="F59" s="7">
-        <v>-5482958</v>
+        <v>17624755</v>
       </c>
       <c r="G59" t="s">
         <v>44</v>
@@ -7294,7 +7454,7 @@
         <v>5</v>
       </c>
       <c r="B60" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C60" t="s">
         <v>118</v>
@@ -7303,10 +7463,10 @@
         <v>600000000</v>
       </c>
       <c r="E60" s="1">
-        <v>687485218</v>
+        <v>690022244</v>
       </c>
       <c r="F60" s="7">
-        <v>-1989098</v>
+        <v>2537026</v>
       </c>
       <c r="G60" t="s">
         <v>44</v>
@@ -7322,7 +7482,7 @@
         <v>5</v>
       </c>
       <c r="B61" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C61" t="s">
         <v>143</v>
@@ -7331,10 +7491,10 @@
         <v>500000000</v>
       </c>
       <c r="E61" s="1">
-        <v>585326949</v>
+        <v>588217306</v>
       </c>
       <c r="F61" s="7">
-        <v>-1842144</v>
+        <v>2890357</v>
       </c>
       <c r="G61" t="s">
         <v>44</v>
@@ -7350,7 +7510,7 @@
         <v>5</v>
       </c>
       <c r="B62" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C62" t="s">
         <v>99</v>
@@ -7359,10 +7519,10 @@
         <v>500000000</v>
       </c>
       <c r="E62" s="1">
-        <v>592402750</v>
+        <v>593879746</v>
       </c>
       <c r="F62" s="7">
-        <v>-1333136</v>
+        <v>1476996</v>
       </c>
       <c r="G62" t="s">
         <v>44</v>
@@ -7378,19 +7538,19 @@
         <v>5</v>
       </c>
       <c r="B63" t="s">
+        <v>148</v>
+      </c>
+      <c r="C63" t="s">
         <v>149</v>
-      </c>
-      <c r="C63" t="s">
-        <v>150</v>
       </c>
       <c r="D63" s="1">
         <v>600000000</v>
       </c>
       <c r="E63" s="1">
-        <v>688857784</v>
+        <v>691679256</v>
       </c>
       <c r="F63" s="7">
-        <v>2896439</v>
+        <v>2821472</v>
       </c>
       <c r="G63" t="s">
         <v>44</v>
@@ -7406,7 +7566,7 @@
         <v>5</v>
       </c>
       <c r="B64" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C64" t="s">
         <v>145</v>
@@ -7415,10 +7575,10 @@
         <v>500000000</v>
       </c>
       <c r="E64" s="1">
-        <v>557844230</v>
+        <v>559691663</v>
       </c>
       <c r="F64" s="7">
-        <v>112413</v>
+        <v>1847433</v>
       </c>
       <c r="G64" t="s">
         <v>44</v>
@@ -7434,7 +7594,7 @@
         <v>5</v>
       </c>
       <c r="B65" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C65" t="s">
         <v>115</v>
@@ -7443,10 +7603,10 @@
         <v>500000000</v>
       </c>
       <c r="E65" s="1">
-        <v>574633525</v>
+        <v>575697957</v>
       </c>
       <c r="F65" s="7">
-        <v>1135897</v>
+        <v>1064432</v>
       </c>
       <c r="G65" t="s">
         <v>44</v>
@@ -7462,19 +7622,19 @@
         <v>5</v>
       </c>
       <c r="B66" t="s">
+        <v>150</v>
+      </c>
+      <c r="C66" t="s">
         <v>151</v>
-      </c>
-      <c r="C66" t="s">
-        <v>152</v>
       </c>
       <c r="D66" s="1">
         <v>400000000</v>
       </c>
       <c r="E66" s="1">
-        <v>532527714</v>
+        <v>547034019</v>
       </c>
       <c r="F66" s="7">
-        <v>-508444</v>
+        <v>14506305</v>
       </c>
       <c r="G66" t="s">
         <v>44</v>
@@ -7484,7 +7644,7 @@
       </c>
       <c r="I66" s="5"/>
       <c r="J66" s="5">
-        <v>0.4351</v>
+        <v>0.47340000000000004</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
@@ -7492,7 +7652,7 @@
         <v>5</v>
       </c>
       <c r="B67" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C67" t="s">
         <v>121</v>
@@ -7501,20 +7661,20 @@
         <v>400000000</v>
       </c>
       <c r="E67" s="1">
-        <v>544159304</v>
+        <v>558820911</v>
       </c>
       <c r="F67" s="7">
-        <v>544159304</v>
+        <v>14661607</v>
       </c>
       <c r="G67" t="s">
-        <v>92</v>
+        <v>44</v>
       </c>
       <c r="H67" t="s">
         <v>96</v>
       </c>
       <c r="I67" s="5"/>
       <c r="J67" s="5">
-        <v>0.4351</v>
+        <v>0.47340000000000004</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
@@ -7522,7 +7682,7 @@
         <v>5</v>
       </c>
       <c r="B68" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C68" t="s">
         <v>105</v>
@@ -7531,10 +7691,10 @@
         <v>400000000</v>
       </c>
       <c r="E68" s="1">
-        <v>546139746</v>
+        <v>560034283</v>
       </c>
       <c r="F68" s="7">
-        <v>1244569</v>
+        <v>13894537</v>
       </c>
       <c r="G68" t="s">
         <v>44</v>
@@ -7544,7 +7704,7 @@
       </c>
       <c r="I68" s="5"/>
       <c r="J68" s="5">
-        <v>0.4351</v>
+        <v>0.47340000000000004</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
@@ -7552,7 +7712,7 @@
         <v>5</v>
       </c>
       <c r="B69" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C69" t="s">
         <v>120</v>
@@ -7561,10 +7721,10 @@
         <v>400000000</v>
       </c>
       <c r="E69" s="1">
-        <v>546102748</v>
+        <v>560172567</v>
       </c>
       <c r="F69" s="7">
-        <v>671977</v>
+        <v>14069819</v>
       </c>
       <c r="G69" t="s">
         <v>44</v>
@@ -7574,7 +7734,7 @@
       </c>
       <c r="I69" s="5"/>
       <c r="J69" s="5">
-        <v>0.4351</v>
+        <v>0.47340000000000004</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
@@ -7582,7 +7742,7 @@
         <v>5</v>
       </c>
       <c r="B70" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C70" t="s">
         <v>79</v>
@@ -7591,10 +7751,10 @@
         <v>400000000</v>
       </c>
       <c r="E70" s="1">
-        <v>450426531</v>
+        <v>436321425</v>
       </c>
       <c r="F70" s="7">
-        <v>12569454</v>
+        <v>-14105106</v>
       </c>
       <c r="G70" t="s">
         <v>44</v>
@@ -7612,19 +7772,19 @@
         <v>5</v>
       </c>
       <c r="B71" t="s">
+        <v>152</v>
+      </c>
+      <c r="C71" t="s">
         <v>153</v>
-      </c>
-      <c r="C71" t="s">
-        <v>154</v>
       </c>
       <c r="D71" s="1">
         <v>400000000</v>
       </c>
       <c r="E71" s="1">
-        <v>458409894</v>
+        <v>444170635</v>
       </c>
       <c r="F71" s="7">
-        <v>12336919</v>
+        <v>-14239259</v>
       </c>
       <c r="G71" t="s">
         <v>44</v>
@@ -7642,7 +7802,7 @@
         <v>5</v>
       </c>
       <c r="B72" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C72" t="s">
         <v>131</v>
@@ -7651,10 +7811,10 @@
         <v>400000000</v>
       </c>
       <c r="E72" s="1">
-        <v>454110042</v>
+        <v>439713582</v>
       </c>
       <c r="F72" s="7">
-        <v>10557301</v>
+        <v>-14396460</v>
       </c>
       <c r="G72" t="s">
         <v>44</v>
@@ -7672,7 +7832,7 @@
         <v>5</v>
       </c>
       <c r="B73" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C73" t="s">
         <v>125</v>
@@ -7681,10 +7841,10 @@
         <v>400000000</v>
       </c>
       <c r="E73" s="1">
-        <v>453176548</v>
+        <v>438001203</v>
       </c>
       <c r="F73" s="7">
-        <v>10798921</v>
+        <v>-15175345</v>
       </c>
       <c r="G73" t="s">
         <v>44</v>
@@ -7702,7 +7862,7 @@
         <v>5</v>
       </c>
       <c r="B74" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C74" t="s">
         <v>79</v>
@@ -7711,10 +7871,10 @@
         <v>400000000</v>
       </c>
       <c r="E74" s="1">
-        <v>423356755</v>
+        <v>434986770</v>
       </c>
       <c r="F74" s="7">
-        <v>3142782</v>
+        <v>11630015</v>
       </c>
       <c r="G74" t="s">
         <v>44</v>
@@ -7724,7 +7884,7 @@
       </c>
       <c r="I74" s="5"/>
       <c r="J74" s="5">
-        <v>0.1043</v>
+        <v>0.1349</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
@@ -7732,19 +7892,19 @@
         <v>5</v>
       </c>
       <c r="B75" t="s">
+        <v>154</v>
+      </c>
+      <c r="C75" t="s">
         <v>155</v>
-      </c>
-      <c r="C75" t="s">
-        <v>156</v>
       </c>
       <c r="D75" s="1">
         <v>400000000</v>
       </c>
       <c r="E75" s="1">
-        <v>421747465</v>
+        <v>433477784</v>
       </c>
       <c r="F75" s="7">
-        <v>2810705</v>
+        <v>11730319</v>
       </c>
       <c r="G75" t="s">
         <v>44</v>
@@ -7754,7 +7914,7 @@
       </c>
       <c r="I75" s="5"/>
       <c r="J75" s="5">
-        <v>0.1043</v>
+        <v>0.1349</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
@@ -7762,7 +7922,7 @@
         <v>5</v>
       </c>
       <c r="B76" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C76" t="s">
         <v>105</v>
@@ -7771,10 +7931,10 @@
         <v>400000000</v>
       </c>
       <c r="E76" s="1">
-        <v>421814640</v>
+        <v>433496207</v>
       </c>
       <c r="F76" s="7">
-        <v>2766191</v>
+        <v>11681567</v>
       </c>
       <c r="G76" t="s">
         <v>44</v>
@@ -7784,7 +7944,7 @@
       </c>
       <c r="I76" s="5"/>
       <c r="J76" s="5">
-        <v>0.1043</v>
+        <v>0.1349</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
@@ -7792,19 +7952,19 @@
         <v>5</v>
       </c>
       <c r="B77" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C77" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D77" s="1">
         <v>400000000</v>
       </c>
       <c r="E77" s="1">
-        <v>422040147</v>
+        <v>433761910</v>
       </c>
       <c r="F77" s="7">
-        <v>2839858</v>
+        <v>11721763</v>
       </c>
       <c r="G77" t="s">
         <v>44</v>
@@ -7814,7 +7974,7 @@
       </c>
       <c r="I77" s="5"/>
       <c r="J77" s="5">
-        <v>0.1043</v>
+        <v>0.1349</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
@@ -7822,7 +7982,7 @@
         <v>6</v>
       </c>
       <c r="B78" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C78" t="s">
         <v>131</v>
@@ -7831,10 +7991,10 @@
         <v>753144454</v>
       </c>
       <c r="E78" s="1">
-        <v>1000473186</v>
+        <v>1020316019</v>
       </c>
       <c r="F78" s="7">
-        <v>-15737222</v>
+        <v>19842833</v>
       </c>
       <c r="G78" t="s">
         <v>44</v>
@@ -7844,7 +8004,7 @@
       </c>
       <c r="I78" s="5"/>
       <c r="J78" s="5">
-        <v>0.2753</v>
+        <v>0.2954</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
@@ -7852,7 +8012,7 @@
         <v>6</v>
       </c>
       <c r="B79" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C79" t="s">
         <v>99</v>
@@ -7861,10 +8021,10 @@
         <v>1003724736</v>
       </c>
       <c r="E79" s="1">
-        <v>955925026</v>
+        <v>960798772</v>
       </c>
       <c r="F79" s="7">
-        <v>-9211812</v>
+        <v>4873746</v>
       </c>
       <c r="G79" t="s">
         <v>44</v>
@@ -7874,7 +8034,7 @@
       </c>
       <c r="I79" s="5"/>
       <c r="J79" s="5">
-        <v>-0.07490000000000001</v>
+        <v>-0.0709</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
@@ -7882,7 +8042,7 @@
         <v>6</v>
       </c>
       <c r="B80" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C80" t="s">
         <v>118</v>
@@ -7891,10 +8051,10 @@
         <v>1018693762</v>
       </c>
       <c r="E80" s="1">
-        <v>951725548</v>
+        <v>955998485</v>
       </c>
       <c r="F80" s="7">
-        <v>-7643783</v>
+        <v>4272937</v>
       </c>
       <c r="G80" t="s">
         <v>44</v>
@@ -7904,7 +8064,7 @@
       </c>
       <c r="I80" s="5"/>
       <c r="J80" s="5">
-        <v>-0.07490000000000001</v>
+        <v>-0.0709</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
@@ -7912,7 +8072,7 @@
         <v>6</v>
       </c>
       <c r="B81" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C81" t="s">
         <v>79</v>
@@ -7921,10 +8081,10 @@
         <v>456987544</v>
       </c>
       <c r="E81" s="1">
-        <v>1504388734</v>
+        <v>1542326350</v>
       </c>
       <c r="F81" s="7">
-        <v>-492790883</v>
+        <v>37937616</v>
       </c>
       <c r="G81" t="s">
         <v>44</v>
@@ -7934,7 +8094,7 @@
       </c>
       <c r="I81" s="5"/>
       <c r="J81" s="5">
-        <v>0.6754000000000001</v>
+        <v>0.7202</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
@@ -7942,7 +8102,7 @@
         <v>6</v>
       </c>
       <c r="B82" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C82" t="s">
         <v>103</v>
@@ -7951,10 +8111,10 @@
         <v>181124998</v>
       </c>
       <c r="E82" s="1">
-        <v>388876019</v>
+        <v>398401997</v>
       </c>
       <c r="F82" s="7">
-        <v>3292095</v>
+        <v>9525978</v>
       </c>
       <c r="G82" t="s">
         <v>44</v>
@@ -7970,7 +8130,7 @@
         <v>6</v>
       </c>
       <c r="B83" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C83" t="s">
         <v>79</v>
@@ -7979,20 +8139,20 @@
         <v>303753501</v>
       </c>
       <c r="E83" s="1">
-        <v>308345333</v>
+        <v>315278070</v>
       </c>
       <c r="F83" s="7">
-        <v>308345333</v>
+        <v>315278070</v>
       </c>
       <c r="G83" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="H83" t="s">
         <v>96</v>
       </c>
       <c r="I83" s="5"/>
       <c r="J83" s="5">
-        <v>0.0174</v>
+        <v>0.0418</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
@@ -8000,7 +8160,7 @@
         <v>6</v>
       </c>
       <c r="B84" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C84" t="s">
         <v>105</v>
@@ -8009,20 +8169,20 @@
         <v>456179013</v>
       </c>
       <c r="E84" s="1">
-        <v>464380516</v>
+        <v>474304460</v>
       </c>
       <c r="F84" s="7">
-        <v>464380516</v>
+        <v>474304460</v>
       </c>
       <c r="G84" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="H84" t="s">
         <v>96</v>
       </c>
       <c r="I84" s="5"/>
       <c r="J84" s="5">
-        <v>0.0174</v>
+        <v>0.0418</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
@@ -8030,29 +8190,29 @@
         <v>6</v>
       </c>
       <c r="B85" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C85" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D85" s="1">
         <v>361201485</v>
       </c>
       <c r="E85" s="1">
-        <v>367521178</v>
+        <v>375878543</v>
       </c>
       <c r="F85" s="7">
-        <v>367521178</v>
+        <v>375878543</v>
       </c>
       <c r="G85" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="H85" t="s">
         <v>96</v>
       </c>
       <c r="I85" s="5"/>
       <c r="J85" s="5">
-        <v>0.0174</v>
+        <v>0.0418</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
@@ -8060,7 +8220,7 @@
         <v>6</v>
       </c>
       <c r="B86" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C86" t="s">
         <v>135</v>
@@ -8069,20 +8229,20 @@
         <v>405779245</v>
       </c>
       <c r="E86" s="1">
-        <v>412290581</v>
+        <v>422143521</v>
       </c>
       <c r="F86" s="7">
-        <v>412290581</v>
+        <v>422143521</v>
       </c>
       <c r="G86" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="H86" t="s">
         <v>96</v>
       </c>
       <c r="I86" s="5"/>
       <c r="J86" s="5">
-        <v>0.0174</v>
+        <v>0.0418</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
@@ -8090,7 +8250,7 @@
         <v>6</v>
       </c>
       <c r="B87" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C87" t="s">
         <v>79</v>
@@ -8099,20 +8259,20 @@
         <v>751993706</v>
       </c>
       <c r="E87" s="1">
-        <v>1013212614</v>
+        <v>1041237914</v>
       </c>
       <c r="F87" s="7">
-        <v>28070705</v>
+        <v>1041237914</v>
       </c>
       <c r="G87" t="s">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="H87" t="s">
         <v>96</v>
       </c>
       <c r="I87" s="5"/>
       <c r="J87" s="5">
-        <v>0.3337</v>
+        <v>0.3711</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
@@ -8120,7 +8280,7 @@
         <v>6</v>
       </c>
       <c r="B88" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C88" t="s">
         <v>113</v>
@@ -8129,10 +8289,10 @@
         <v>414056068</v>
       </c>
       <c r="E88" s="1">
-        <v>485988414</v>
+        <v>478897741</v>
       </c>
       <c r="F88" s="7">
-        <v>-1144086</v>
+        <v>-7090673</v>
       </c>
       <c r="G88" t="s">
         <v>44</v>
@@ -8142,7 +8302,7 @@
       </c>
       <c r="I88" s="5"/>
       <c r="J88" s="5">
-        <v>0.5083</v>
+        <v>0.5336</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
@@ -8150,7 +8310,7 @@
         <v>6</v>
       </c>
       <c r="B89" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C89" t="s">
         <v>114</v>
@@ -8159,10 +8319,10 @@
         <v>315296707</v>
       </c>
       <c r="E89" s="1">
-        <v>485100246</v>
+        <v>488403338</v>
       </c>
       <c r="F89" s="7">
-        <v>18202137</v>
+        <v>3303092</v>
       </c>
       <c r="G89" t="s">
         <v>44</v>
@@ -8172,7 +8332,7 @@
       </c>
       <c r="I89" s="5"/>
       <c r="J89" s="5">
-        <v>0.5083</v>
+        <v>0.5336</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
@@ -8180,7 +8340,7 @@
         <v>6</v>
       </c>
       <c r="B90" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C90" t="s">
         <v>115</v>
@@ -8189,10 +8349,10 @@
         <v>704502354</v>
       </c>
       <c r="E90" s="1">
-        <v>1076341328</v>
+        <v>1085299191</v>
       </c>
       <c r="F90" s="7">
-        <v>35929266</v>
+        <v>8957863</v>
       </c>
       <c r="G90" t="s">
         <v>44</v>
@@ -8202,7 +8362,7 @@
       </c>
       <c r="I90" s="5"/>
       <c r="J90" s="5">
-        <v>0.5083</v>
+        <v>0.5336</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
@@ -8210,19 +8370,19 @@
         <v>6</v>
       </c>
       <c r="B91" t="s">
+        <v>164</v>
+      </c>
+      <c r="C91" t="s">
         <v>165</v>
-      </c>
-      <c r="C91" t="s">
-        <v>166</v>
       </c>
       <c r="D91" s="1">
         <v>954418976</v>
       </c>
       <c r="E91" s="1">
-        <v>1388520134</v>
+        <v>1365207396</v>
       </c>
       <c r="F91" s="7">
-        <v>-4372508</v>
+        <v>-23312738</v>
       </c>
       <c r="G91" t="s">
         <v>44</v>
@@ -8232,7 +8392,7 @@
       </c>
       <c r="I91" s="5"/>
       <c r="J91" s="5">
-        <v>0.4003</v>
+        <v>0.37420000000000003</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
@@ -8240,19 +8400,19 @@
         <v>6</v>
       </c>
       <c r="B92" t="s">
+        <v>166</v>
+      </c>
+      <c r="C92" t="s">
         <v>167</v>
-      </c>
-      <c r="C92" t="s">
-        <v>168</v>
       </c>
       <c r="D92" s="1">
         <v>708888643</v>
       </c>
       <c r="E92" s="1">
-        <v>801020312</v>
+        <v>779570218</v>
       </c>
       <c r="F92" s="7">
-        <v>17805307</v>
+        <v>-21450094</v>
       </c>
       <c r="G92" t="s">
         <v>44</v>
@@ -8268,22 +8428,22 @@
         <v>6</v>
       </c>
       <c r="B93" t="s">
+        <v>168</v>
+      </c>
+      <c r="C93" t="s">
         <v>169</v>
-      </c>
-      <c r="C93" t="s">
-        <v>170</v>
       </c>
       <c r="D93" s="1">
         <v>275923278</v>
       </c>
       <c r="E93" s="1">
-        <v>275639320</v>
+        <v>286025127</v>
       </c>
       <c r="F93" s="7">
-        <v>275639320</v>
+        <v>10385807</v>
       </c>
       <c r="G93" t="s">
-        <v>92</v>
+        <v>44</v>
       </c>
       <c r="H93" t="s">
         <v>96</v>
@@ -8296,7 +8456,7 @@
         <v>6</v>
       </c>
       <c r="B94" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C94" t="s">
         <v>101</v>
@@ -8305,13 +8465,13 @@
         <v>440558255</v>
       </c>
       <c r="E94" s="1">
-        <v>442701115</v>
+        <v>452543643</v>
       </c>
       <c r="F94" s="7">
-        <v>442701115</v>
+        <v>9842528</v>
       </c>
       <c r="G94" t="s">
-        <v>92</v>
+        <v>44</v>
       </c>
       <c r="H94" t="s">
         <v>96</v>
@@ -8324,7 +8484,7 @@
         <v>6</v>
       </c>
       <c r="B95" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C95" t="s">
         <v>128</v>
@@ -8333,13 +8493,13 @@
         <v>443166315</v>
       </c>
       <c r="E95" s="1">
-        <v>446332480</v>
+        <v>452972950</v>
       </c>
       <c r="F95" s="7">
-        <v>446332480</v>
+        <v>6640470</v>
       </c>
       <c r="G95" t="s">
-        <v>92</v>
+        <v>44</v>
       </c>
       <c r="H95" t="s">
         <v>96</v>
@@ -8361,10 +8521,10 @@
         <v>127303524</v>
       </c>
       <c r="E96" s="1">
-        <v>243246878</v>
+        <v>251704839</v>
       </c>
       <c r="F96" s="7">
-        <v>-903402</v>
+        <v>8457961</v>
       </c>
       <c r="G96" t="s">
         <v>44</v>
@@ -8374,7 +8534,7 @@
       </c>
       <c r="I96" s="5"/>
       <c r="J96" s="5">
-        <v>0.914</v>
+        <v>0.9765</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
@@ -8391,10 +8551,10 @@
         <v>147528441</v>
       </c>
       <c r="E97" s="1">
-        <v>288944122</v>
+        <v>297801427</v>
       </c>
       <c r="F97" s="7">
-        <v>-305339</v>
+        <v>8857305</v>
       </c>
       <c r="G97" t="s">
         <v>44</v>
@@ -8404,7 +8564,7 @@
       </c>
       <c r="I97" s="5"/>
       <c r="J97" s="5">
-        <v>0.914</v>
+        <v>0.9765</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
@@ -8421,10 +8581,10 @@
         <v>157982595</v>
       </c>
       <c r="E98" s="1">
-        <v>308803058</v>
+        <v>318477456</v>
       </c>
       <c r="F98" s="7">
-        <v>-423848</v>
+        <v>9674398</v>
       </c>
       <c r="G98" t="s">
         <v>44</v>
@@ -8434,7 +8594,7 @@
       </c>
       <c r="I98" s="5"/>
       <c r="J98" s="5">
-        <v>0.914</v>
+        <v>0.9765</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
@@ -8451,10 +8611,10 @@
         <v>158484700</v>
       </c>
       <c r="E99" s="1">
-        <v>306792507</v>
+        <v>316304363</v>
       </c>
       <c r="F99" s="7">
-        <v>-754352</v>
+        <v>9511856</v>
       </c>
       <c r="G99" t="s">
         <v>44</v>
@@ -8464,7 +8624,7 @@
       </c>
       <c r="I99" s="5"/>
       <c r="J99" s="5">
-        <v>0.914</v>
+        <v>0.9765</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
@@ -8481,10 +8641,10 @@
         <v>319635794</v>
       </c>
       <c r="E100" s="1">
-        <v>391326795</v>
+        <v>392940001</v>
       </c>
       <c r="F100" s="7">
-        <v>381026</v>
+        <v>1613206</v>
       </c>
       <c r="G100" t="s">
         <v>44</v>
@@ -8509,10 +8669,10 @@
         <v>279785344</v>
       </c>
       <c r="E101" s="1">
-        <v>361976287</v>
+        <v>363148480</v>
       </c>
       <c r="F101" s="7">
-        <v>695834</v>
+        <v>1172193</v>
       </c>
       <c r="G101" t="s">
         <v>44</v>
@@ -8537,10 +8697,10 @@
         <v>328000470</v>
       </c>
       <c r="E102" s="1">
-        <v>409014201</v>
+        <v>410447072</v>
       </c>
       <c r="F102" s="7">
-        <v>147161</v>
+        <v>1432871</v>
       </c>
       <c r="G102" t="s">
         <v>44</v>
@@ -8556,7 +8716,7 @@
         <v>6</v>
       </c>
       <c r="B103" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C103" t="s">
         <v>103</v>
@@ -8565,10 +8725,10 @@
         <v>116977839</v>
       </c>
       <c r="E103" s="1">
-        <v>187362563</v>
+        <v>188920404</v>
       </c>
       <c r="F103" s="7">
-        <v>3027644</v>
+        <v>1557841</v>
       </c>
       <c r="G103" t="s">
         <v>44</v>
@@ -8584,7 +8744,7 @@
         <v>6</v>
       </c>
       <c r="B104" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C104" t="s">
         <v>115</v>
@@ -8593,10 +8753,10 @@
         <v>107476614</v>
       </c>
       <c r="E104" s="1">
-        <v>145514023</v>
+        <v>147100860</v>
       </c>
       <c r="F104" s="7">
-        <v>1149442</v>
+        <v>1586837</v>
       </c>
       <c r="G104" t="s">
         <v>44</v>
@@ -8612,7 +8772,7 @@
         <v>6</v>
       </c>
       <c r="B105" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C105" t="s">
         <v>134</v>
@@ -8621,10 +8781,10 @@
         <v>115110097</v>
       </c>
       <c r="E105" s="1">
-        <v>167820235</v>
+        <v>172703210</v>
       </c>
       <c r="F105" s="7">
-        <v>1264593</v>
+        <v>4882975</v>
       </c>
       <c r="G105" t="s">
         <v>44</v>
@@ -8649,10 +8809,10 @@
         <v>60000000</v>
       </c>
       <c r="E106" s="1">
-        <v>82391662</v>
+        <v>81154165</v>
       </c>
       <c r="F106" s="7">
-        <v>-283260</v>
+        <v>-1237497</v>
       </c>
       <c r="G106" t="s">
         <v>44</v>
@@ -8662,7 +8822,7 @@
       </c>
       <c r="I106" s="5"/>
       <c r="J106" s="5">
-        <v>0.39909999999999995</v>
+        <v>0.3736</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
@@ -8679,10 +8839,10 @@
         <v>60000000</v>
       </c>
       <c r="E107" s="1">
-        <v>90179012</v>
+        <v>88847965</v>
       </c>
       <c r="F107" s="7">
-        <v>-171763</v>
+        <v>-1331047</v>
       </c>
       <c r="G107" t="s">
         <v>44</v>
@@ -8692,7 +8852,7 @@
       </c>
       <c r="I107" s="5"/>
       <c r="J107" s="5">
-        <v>0.39909999999999995</v>
+        <v>0.3736</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
@@ -8709,10 +8869,10 @@
         <v>60000000</v>
       </c>
       <c r="E108" s="1">
-        <v>73920654</v>
+        <v>72127590</v>
       </c>
       <c r="F108" s="7">
-        <v>-869016</v>
+        <v>-1793064</v>
       </c>
       <c r="G108" t="s">
         <v>44</v>
@@ -8722,7 +8882,7 @@
       </c>
       <c r="I108" s="5"/>
       <c r="J108" s="5">
-        <v>0.39909999999999995</v>
+        <v>0.3736</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
@@ -8739,10 +8899,10 @@
         <v>60000000</v>
       </c>
       <c r="E109" s="1">
-        <v>83221636</v>
+        <v>81811979</v>
       </c>
       <c r="F109" s="7">
-        <v>996985</v>
+        <v>-1409657</v>
       </c>
       <c r="G109" t="s">
         <v>44</v>
@@ -8752,7 +8912,7 @@
       </c>
       <c r="I109" s="5"/>
       <c r="J109" s="5">
-        <v>0.39909999999999995</v>
+        <v>0.3736</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
@@ -8760,7 +8920,7 @@
         <v>7</v>
       </c>
       <c r="B110" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C110" t="s">
         <v>114</v>
@@ -8769,20 +8929,20 @@
         <v>946084601</v>
       </c>
       <c r="E110" s="1">
-        <v>1255172172</v>
+        <v>1290575372</v>
       </c>
       <c r="F110" s="7">
-        <v>86029794</v>
+        <v>1290575372</v>
       </c>
       <c r="G110" t="s">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="H110" t="s">
         <v>96</v>
       </c>
       <c r="I110" s="5"/>
       <c r="J110" s="5">
-        <v>0.6374</v>
+        <v>0.6796</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
@@ -8790,7 +8950,7 @@
         <v>7</v>
       </c>
       <c r="B111" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C111" t="s">
         <v>97</v>
@@ -8799,20 +8959,20 @@
         <v>274323144</v>
       </c>
       <c r="E111" s="1">
-        <v>374599171</v>
+        <v>377268078</v>
       </c>
       <c r="F111" s="7">
-        <v>-1221560</v>
+        <v>377268078</v>
       </c>
       <c r="G111" t="s">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="H111" t="s">
         <v>96</v>
       </c>
       <c r="I111" s="5"/>
       <c r="J111" s="5">
-        <v>0.36829999999999996</v>
+        <v>0.3799</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
@@ -8820,7 +8980,7 @@
         <v>7</v>
       </c>
       <c r="B112" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C112" t="s">
         <v>115</v>
@@ -8829,20 +8989,20 @@
         <v>314964360</v>
       </c>
       <c r="E112" s="1">
-        <v>337505230</v>
+        <v>338757123</v>
       </c>
       <c r="F112" s="7">
-        <v>-2653247</v>
+        <v>338757123</v>
       </c>
       <c r="G112" t="s">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="H112" t="s">
         <v>96</v>
       </c>
       <c r="I112" s="5"/>
       <c r="J112" s="5">
-        <v>0.0633</v>
+        <v>0.0679</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
@@ -8850,7 +9010,7 @@
         <v>7</v>
       </c>
       <c r="B113" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C113" t="s">
         <v>99</v>
@@ -8859,20 +9019,20 @@
         <v>1151650255</v>
       </c>
       <c r="E113" s="1">
-        <v>1214682638</v>
+        <v>1221279018</v>
       </c>
       <c r="F113" s="7">
-        <v>-11725692</v>
+        <v>1221279018</v>
       </c>
       <c r="G113" t="s">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="H113" t="s">
         <v>96</v>
       </c>
       <c r="I113" s="5"/>
       <c r="J113" s="5">
-        <v>0.0633</v>
+        <v>0.0679</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
@@ -8880,7 +9040,7 @@
         <v>7</v>
       </c>
       <c r="B114" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C114" t="s">
         <v>120</v>
@@ -8889,10 +9049,10 @@
         <v>823846300</v>
       </c>
       <c r="E114" s="1">
-        <v>997557132</v>
+        <v>1021621197</v>
       </c>
       <c r="F114" s="7">
-        <v>-18297135</v>
+        <v>24064065</v>
       </c>
       <c r="G114" t="s">
         <v>44</v>
@@ -8902,7 +9062,7 @@
       </c>
       <c r="I114" s="5"/>
       <c r="J114" s="5">
-        <v>0.21989999999999998</v>
+        <v>0.2486</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.25">
@@ -8910,7 +9070,7 @@
         <v>7</v>
       </c>
       <c r="B115" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C115" t="s">
         <v>121</v>
@@ -8919,10 +9079,10 @@
         <v>820369757</v>
       </c>
       <c r="E115" s="1">
-        <v>988168804</v>
+        <v>1010965676</v>
       </c>
       <c r="F115" s="7">
-        <v>-15019704</v>
+        <v>22796872</v>
       </c>
       <c r="G115" t="s">
         <v>44</v>
@@ -8932,7 +9092,7 @@
       </c>
       <c r="I115" s="5"/>
       <c r="J115" s="5">
-        <v>0.21989999999999998</v>
+        <v>0.2486</v>
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
@@ -8940,7 +9100,7 @@
         <v>7</v>
       </c>
       <c r="B116" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C116" t="s">
         <v>122</v>
@@ -8949,10 +9109,10 @@
         <v>822731626</v>
       </c>
       <c r="E116" s="1">
-        <v>993985391</v>
+        <v>1018253169</v>
       </c>
       <c r="F116" s="7">
-        <v>-17743111</v>
+        <v>24267778</v>
       </c>
       <c r="G116" t="s">
         <v>44</v>
@@ -8962,7 +9122,7 @@
       </c>
       <c r="I116" s="5"/>
       <c r="J116" s="5">
-        <v>0.21989999999999998</v>
+        <v>0.2486</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
@@ -8970,7 +9130,7 @@
         <v>7</v>
       </c>
       <c r="B117" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C117" t="s">
         <v>135</v>
@@ -8979,10 +9139,10 @@
         <v>425389351</v>
       </c>
       <c r="E117" s="1">
-        <v>475239009</v>
+        <v>468512558</v>
       </c>
       <c r="F117" s="7">
-        <v>9432028</v>
+        <v>-6726451</v>
       </c>
       <c r="G117" t="s">
         <v>44</v>
@@ -8992,7 +9152,7 @@
       </c>
       <c r="I117" s="5"/>
       <c r="J117" s="5">
-        <v>0.1247</v>
+        <v>0.10369999999999999</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
@@ -9000,7 +9160,7 @@
         <v>7</v>
       </c>
       <c r="B118" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C118" t="s">
         <v>124</v>
@@ -9009,10 +9169,10 @@
         <v>508571279</v>
       </c>
       <c r="E118" s="1">
-        <v>578473784</v>
+        <v>567503308</v>
       </c>
       <c r="F118" s="7">
-        <v>1973545</v>
+        <v>-10970476</v>
       </c>
       <c r="G118" t="s">
         <v>44</v>
@@ -9022,7 +9182,7 @@
       </c>
       <c r="I118" s="5"/>
       <c r="J118" s="5">
-        <v>0.1247</v>
+        <v>0.10369999999999999</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
@@ -9030,7 +9190,7 @@
         <v>7</v>
       </c>
       <c r="B119" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C119" t="s">
         <v>125</v>
@@ -9039,10 +9199,10 @@
         <v>464478952</v>
       </c>
       <c r="E119" s="1">
-        <v>511250642</v>
+        <v>500368737</v>
       </c>
       <c r="F119" s="7">
-        <v>-186646</v>
+        <v>-10881905</v>
       </c>
       <c r="G119" t="s">
         <v>44</v>
@@ -9052,7 +9212,7 @@
       </c>
       <c r="I119" s="5"/>
       <c r="J119" s="5">
-        <v>0.1247</v>
+        <v>0.10369999999999999</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
@@ -9060,7 +9220,7 @@
         <v>7</v>
       </c>
       <c r="B120" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C120" t="s">
         <v>140</v>
@@ -9069,10 +9229,10 @@
         <v>627191291</v>
       </c>
       <c r="E120" s="1">
-        <v>714504487</v>
+        <v>694551985</v>
       </c>
       <c r="F120" s="7">
-        <v>18107712</v>
+        <v>-19952502</v>
       </c>
       <c r="G120" t="s">
         <v>44</v>
@@ -9082,7 +9242,7 @@
       </c>
       <c r="I120" s="5"/>
       <c r="J120" s="5">
-        <v>0.1307</v>
+        <v>0.096</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
@@ -9090,19 +9250,19 @@
         <v>7</v>
       </c>
       <c r="B121" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C121" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D121" s="1">
         <v>425091462</v>
       </c>
       <c r="E121" s="1">
-        <v>478192278</v>
+        <v>465441658</v>
       </c>
       <c r="F121" s="7">
-        <v>10642444</v>
+        <v>-12750620</v>
       </c>
       <c r="G121" t="s">
         <v>44</v>
@@ -9112,7 +9272,7 @@
       </c>
       <c r="I121" s="5"/>
       <c r="J121" s="5">
-        <v>0.1307</v>
+        <v>0.096</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
@@ -9120,7 +9280,7 @@
         <v>7</v>
       </c>
       <c r="B122" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C122" t="s">
         <v>101</v>
@@ -9129,13 +9289,13 @@
         <v>428950000</v>
       </c>
       <c r="E122" s="1">
-        <v>431428553</v>
+        <v>441090952</v>
       </c>
       <c r="F122" s="7">
-        <v>431428553</v>
+        <v>9662399</v>
       </c>
       <c r="G122" t="s">
-        <v>92</v>
+        <v>44</v>
       </c>
       <c r="H122" t="s">
         <v>96</v>
@@ -9148,7 +9308,7 @@
         <v>7</v>
       </c>
       <c r="B123" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C123" t="s">
         <v>128</v>
@@ -9157,13 +9317,13 @@
         <v>462463907</v>
       </c>
       <c r="E123" s="1">
-        <v>466146222</v>
+        <v>473050285</v>
       </c>
       <c r="F123" s="7">
-        <v>466146222</v>
+        <v>6904063</v>
       </c>
       <c r="G123" t="s">
-        <v>92</v>
+        <v>44</v>
       </c>
       <c r="H123" t="s">
         <v>96</v>
@@ -9182,23 +9342,23 @@
         <v>79</v>
       </c>
       <c r="D124" s="1">
-        <v>151969815</v>
+        <v>274819596</v>
       </c>
       <c r="E124" s="1">
-        <v>266710574</v>
+        <v>276121459</v>
       </c>
       <c r="F124" s="7">
-        <v>-10002997</v>
+        <v>276121459</v>
       </c>
       <c r="G124" t="s">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="H124" t="s">
         <v>96</v>
       </c>
       <c r="I124" s="5"/>
       <c r="J124" s="5">
-        <v>0.6866</v>
+        <v>0.0045000000000000005</v>
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.25">
@@ -9215,10 +9375,10 @@
         <v>105992843</v>
       </c>
       <c r="E125" s="1">
-        <v>129828838</v>
+        <v>130364344</v>
       </c>
       <c r="F125" s="7">
-        <v>127284</v>
+        <v>535506</v>
       </c>
       <c r="G125" t="s">
         <v>44</v>
@@ -9243,10 +9403,10 @@
         <v>258094745</v>
       </c>
       <c r="E126" s="1">
-        <v>333870078</v>
+        <v>334990484</v>
       </c>
       <c r="F126" s="7">
-        <v>649752</v>
+        <v>1120406</v>
       </c>
       <c r="G126" t="s">
         <v>44</v>
@@ -9271,10 +9431,10 @@
         <v>299312934</v>
       </c>
       <c r="E127" s="1">
-        <v>373139760</v>
+        <v>374421686</v>
       </c>
       <c r="F127" s="7">
-        <v>61623</v>
+        <v>1281926</v>
       </c>
       <c r="G127" t="s">
         <v>44</v>
@@ -9290,7 +9450,7 @@
         <v>8</v>
       </c>
       <c r="B128" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C128" t="s">
         <v>120</v>
@@ -9299,10 +9459,10 @@
         <v>510820499</v>
       </c>
       <c r="E128" s="1">
-        <v>619202327</v>
+        <v>634097678</v>
       </c>
       <c r="F128" s="7">
-        <v>-11343656</v>
+        <v>14895351</v>
       </c>
       <c r="G128" t="s">
         <v>44</v>
@@ -9312,7 +9472,7 @@
       </c>
       <c r="I128" s="5"/>
       <c r="J128" s="5">
-        <v>0.21989999999999998</v>
+        <v>0.2486</v>
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.25">
@@ -9320,7 +9480,7 @@
         <v>8</v>
       </c>
       <c r="B129" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C129" t="s">
         <v>121</v>
@@ -9329,10 +9489,10 @@
         <v>508402028</v>
       </c>
       <c r="E129" s="1">
-        <v>612836264</v>
+        <v>626985710</v>
       </c>
       <c r="F129" s="7">
-        <v>-9349078</v>
+        <v>14149446</v>
       </c>
       <c r="G129" t="s">
         <v>44</v>
@@ -9342,7 +9502,7 @@
       </c>
       <c r="I129" s="5"/>
       <c r="J129" s="5">
-        <v>0.21989999999999998</v>
+        <v>0.2486</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.25">
@@ -9350,7 +9510,7 @@
         <v>8</v>
       </c>
       <c r="B130" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C130" t="s">
         <v>140</v>
@@ -9359,10 +9519,10 @@
         <v>378735074</v>
       </c>
       <c r="E130" s="1">
-        <v>430909955</v>
+        <v>418877022</v>
       </c>
       <c r="F130" s="7">
-        <v>10920693</v>
+        <v>-12032933</v>
       </c>
       <c r="G130" t="s">
         <v>44</v>
@@ -9372,7 +9532,7 @@
       </c>
       <c r="I130" s="5"/>
       <c r="J130" s="5">
-        <v>0.1307</v>
+        <v>0.096</v>
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.25">
@@ -9389,20 +9549,20 @@
         <v>339081835</v>
       </c>
       <c r="E131" s="1">
-        <v>334549088</v>
+        <v>338046626</v>
       </c>
       <c r="F131" s="7">
-        <v>334549088</v>
+        <v>338046626</v>
       </c>
       <c r="G131" t="s">
-        <v>92</v>
+        <v>44</v>
       </c>
       <c r="H131" t="s">
         <v>96</v>
       </c>
       <c r="I131" s="5"/>
       <c r="J131" s="5">
-        <v>-0.0173</v>
+        <v>-0.0072</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.25">
@@ -9416,23 +9576,23 @@
         <v>79</v>
       </c>
       <c r="D132" s="1">
-        <v>151227051</v>
+        <v>273185052</v>
       </c>
       <c r="E132" s="1">
-        <v>265114862</v>
+        <v>274487008</v>
       </c>
       <c r="F132" s="7">
-        <v>-9882162</v>
+        <v>274487008</v>
       </c>
       <c r="G132" t="s">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="H132" t="s">
         <v>96</v>
       </c>
       <c r="I132" s="5"/>
       <c r="J132" s="5">
-        <v>0.6866</v>
+        <v>0.0045000000000000005</v>
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.25">
@@ -9449,10 +9609,10 @@
         <v>159277445</v>
       </c>
       <c r="E133" s="1">
-        <v>304979599</v>
+        <v>315509253</v>
       </c>
       <c r="F133" s="7">
-        <v>-1188805</v>
+        <v>10529654</v>
       </c>
       <c r="G133" t="s">
         <v>44</v>
@@ -9462,7 +9622,7 @@
       </c>
       <c r="I133" s="5"/>
       <c r="J133" s="5">
-        <v>0.914</v>
+        <v>0.9765</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.25">
@@ -9479,10 +9639,10 @@
         <v>159101214</v>
       </c>
       <c r="E134" s="1">
-        <v>311496128</v>
+        <v>321077554</v>
       </c>
       <c r="F134" s="7">
-        <v>-330845</v>
+        <v>9581426</v>
       </c>
       <c r="G134" t="s">
         <v>44</v>
@@ -9492,7 +9652,7 @@
       </c>
       <c r="I134" s="5"/>
       <c r="J134" s="5">
-        <v>0.914</v>
+        <v>0.9765</v>
       </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.25">
@@ -9509,10 +9669,10 @@
         <v>159382615</v>
       </c>
       <c r="E135" s="1">
-        <v>311580226</v>
+        <v>321447801</v>
       </c>
       <c r="F135" s="7">
-        <v>-493569</v>
+        <v>9867575</v>
       </c>
       <c r="G135" t="s">
         <v>44</v>
@@ -9522,7 +9682,7 @@
       </c>
       <c r="I135" s="5"/>
       <c r="J135" s="5">
-        <v>0.914</v>
+        <v>0.9765</v>
       </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.25">
@@ -9539,10 +9699,10 @@
         <v>159708987</v>
       </c>
       <c r="E136" s="1">
-        <v>309819784</v>
+        <v>319458671</v>
       </c>
       <c r="F136" s="7">
-        <v>-813461</v>
+        <v>9638887</v>
       </c>
       <c r="G136" t="s">
         <v>44</v>
@@ -9552,7 +9712,7 @@
       </c>
       <c r="I136" s="5"/>
       <c r="J136" s="5">
-        <v>0.914</v>
+        <v>0.9765</v>
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.25">
@@ -9569,10 +9729,10 @@
         <v>106848757</v>
       </c>
       <c r="E137" s="1">
-        <v>130862848</v>
+        <v>131401246</v>
       </c>
       <c r="F137" s="7">
-        <v>124527</v>
+        <v>538398</v>
       </c>
       <c r="G137" t="s">
         <v>44</v>
@@ -9597,10 +9757,10 @@
         <v>134102607</v>
       </c>
       <c r="E138" s="1">
-        <v>174702263</v>
+        <v>175274498</v>
       </c>
       <c r="F138" s="7">
-        <v>342198</v>
+        <v>572235</v>
       </c>
       <c r="G138" t="s">
         <v>44</v>
@@ -9625,10 +9785,10 @@
         <v>257027478</v>
       </c>
       <c r="E139" s="1">
-        <v>319545179</v>
+        <v>320650288</v>
       </c>
       <c r="F139" s="7">
-        <v>142366</v>
+        <v>1105109</v>
       </c>
       <c r="G139" t="s">
         <v>44</v>
@@ -9644,7 +9804,7 @@
         <v>8</v>
       </c>
       <c r="B140" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C140" t="s">
         <v>103</v>
@@ -9653,10 +9813,10 @@
         <v>160873068</v>
       </c>
       <c r="E140" s="1">
-        <v>257650149</v>
+        <v>259787993</v>
       </c>
       <c r="F140" s="7">
-        <v>4148152</v>
+        <v>2137844</v>
       </c>
       <c r="G140" t="s">
         <v>44</v>
@@ -9672,7 +9832,7 @@
         <v>8</v>
       </c>
       <c r="B141" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C141" t="s">
         <v>115</v>
@@ -9681,10 +9841,10 @@
         <v>163472383</v>
       </c>
       <c r="E141" s="1">
-        <v>221410107</v>
+        <v>223832329</v>
       </c>
       <c r="F141" s="7">
-        <v>1745193</v>
+        <v>2422222</v>
       </c>
       <c r="G141" t="s">
         <v>44</v>
@@ -9700,7 +9860,7 @@
         <v>8</v>
       </c>
       <c r="B142" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C142" t="s">
         <v>134</v>
@@ -9709,10 +9869,10 @@
         <v>161120051</v>
       </c>
       <c r="E142" s="1">
-        <v>234838962</v>
+        <v>241677340</v>
       </c>
       <c r="F142" s="7">
-        <v>1796960</v>
+        <v>6838378</v>
       </c>
       <c r="G142" t="s">
         <v>44</v>
@@ -9728,7 +9888,7 @@
         <v>8</v>
       </c>
       <c r="B143" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C143" t="s">
         <v>105</v>
@@ -9737,10 +9897,10 @@
         <v>149737366</v>
       </c>
       <c r="E143" s="1">
-        <v>220527203</v>
+        <v>223233473</v>
       </c>
       <c r="F143" s="7">
-        <v>10349727</v>
+        <v>2706270</v>
       </c>
       <c r="G143" t="s">
         <v>44</v>
@@ -9765,10 +9925,10 @@
         <v>170770415</v>
       </c>
       <c r="E144" s="1">
-        <v>169160821</v>
+        <v>169885181</v>
       </c>
       <c r="F144" s="7">
-        <v>-2713085</v>
+        <v>724360</v>
       </c>
       <c r="G144" t="s">
         <v>44</v>
@@ -9778,7 +9938,7 @@
       </c>
       <c r="I144" s="5"/>
       <c r="J144" s="5">
-        <v>-0.0070999999999999995</v>
+        <v>-0.003</v>
       </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.25">
@@ -9795,10 +9955,10 @@
         <v>92866928</v>
       </c>
       <c r="E145" s="1">
-        <v>92150680</v>
+        <v>92519452</v>
       </c>
       <c r="F145" s="7">
-        <v>-1474945</v>
+        <v>368772</v>
       </c>
       <c r="G145" t="s">
         <v>44</v>
@@ -9808,7 +9968,7 @@
       </c>
       <c r="I145" s="5"/>
       <c r="J145" s="5">
-        <v>-0.0070999999999999995</v>
+        <v>-0.003</v>
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.25">
@@ -9825,10 +9985,10 @@
         <v>116515080</v>
       </c>
       <c r="E146" s="1">
-        <v>115478381</v>
+        <v>115860027</v>
       </c>
       <c r="F146" s="7">
-        <v>-1835166</v>
+        <v>381646</v>
       </c>
       <c r="G146" t="s">
         <v>44</v>
@@ -9838,7 +9998,7 @@
       </c>
       <c r="I146" s="5"/>
       <c r="J146" s="5">
-        <v>-0.0070999999999999995</v>
+        <v>-0.003</v>
       </c>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.25">
@@ -9855,10 +10015,10 @@
         <v>60000000</v>
       </c>
       <c r="E147" s="1">
-        <v>76839686</v>
+        <v>78475187</v>
       </c>
       <c r="F147" s="7">
-        <v>-2121898</v>
+        <v>1635501</v>
       </c>
       <c r="G147" t="s">
         <v>44</v>
@@ -9883,10 +10043,10 @@
         <v>60000000</v>
       </c>
       <c r="E148" s="1">
-        <v>72935938</v>
+        <v>74567057</v>
       </c>
       <c r="F148" s="7">
-        <v>-73692729</v>
+        <v>-145161114</v>
       </c>
       <c r="G148" t="s">
         <v>44</v>
@@ -9911,10 +10071,10 @@
         <v>120000000</v>
       </c>
       <c r="E149" s="1">
-        <v>146792233</v>
+        <v>150054926</v>
       </c>
       <c r="F149" s="7">
-        <v>163566</v>
+        <v>-69673245</v>
       </c>
       <c r="G149" t="s">
         <v>44</v>
@@ -9939,10 +10099,10 @@
         <v>100000000</v>
       </c>
       <c r="E150" s="1">
-        <v>133483168</v>
+        <v>135778058</v>
       </c>
       <c r="F150" s="7">
-        <v>-25400</v>
+        <v>2294890</v>
       </c>
       <c r="G150" t="s">
         <v>44</v>
@@ -9967,10 +10127,10 @@
         <v>60000000</v>
       </c>
       <c r="E151" s="1">
-        <v>75654265</v>
+        <v>77710665</v>
       </c>
       <c r="F151" s="7">
-        <v>-485923</v>
+        <v>2056400</v>
       </c>
       <c r="G151" t="s">
         <v>44</v>
@@ -9986,7 +10146,7 @@
         <v>8</v>
       </c>
       <c r="B152" t="s">
-        <v>178</v>
+        <v>146</v>
       </c>
       <c r="C152" t="s">
         <v>59</v>
@@ -9995,20 +10155,20 @@
         <v>60000000</v>
       </c>
       <c r="E152" s="1">
-        <v>89122293</v>
+        <v>91361493</v>
       </c>
       <c r="F152" s="7">
-        <v>-1236575</v>
+        <v>91361493</v>
       </c>
       <c r="G152" t="s">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="H152" t="s">
         <v>96</v>
       </c>
       <c r="I152" s="5"/>
       <c r="J152" s="5">
-        <v>0.7315</v>
+        <v>0.7886</v>
       </c>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.25">
@@ -10016,7 +10176,7 @@
         <v>8</v>
       </c>
       <c r="B153" t="s">
-        <v>178</v>
+        <v>146</v>
       </c>
       <c r="C153" t="s">
         <v>121</v>
@@ -10025,20 +10185,20 @@
         <v>60000000</v>
       </c>
       <c r="E153" s="1">
-        <v>85570319</v>
+        <v>88433005</v>
       </c>
       <c r="F153" s="7">
-        <v>-950764</v>
+        <v>88433005</v>
       </c>
       <c r="G153" t="s">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="H153" t="s">
         <v>96</v>
       </c>
       <c r="I153" s="5"/>
       <c r="J153" s="5">
-        <v>0.7315</v>
+        <v>0.7886</v>
       </c>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.25">
@@ -10046,29 +10206,29 @@
         <v>8</v>
       </c>
       <c r="B154" t="s">
-        <v>178</v>
+        <v>146</v>
       </c>
       <c r="C154" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D154" s="1">
         <v>60000000</v>
       </c>
       <c r="E154" s="1">
-        <v>87308547</v>
+        <v>89494700</v>
       </c>
       <c r="F154" s="7">
-        <v>-471520</v>
+        <v>89494700</v>
       </c>
       <c r="G154" t="s">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="H154" t="s">
         <v>96</v>
       </c>
       <c r="I154" s="5"/>
       <c r="J154" s="5">
-        <v>0.7315</v>
+        <v>0.7886</v>
       </c>
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.25">
@@ -10076,7 +10236,7 @@
         <v>8</v>
       </c>
       <c r="B155" t="s">
-        <v>178</v>
+        <v>146</v>
       </c>
       <c r="C155" t="s">
         <v>144</v>
@@ -10085,20 +10245,20 @@
         <v>60000000</v>
       </c>
       <c r="E155" s="1">
-        <v>84636837</v>
+        <v>87312043</v>
       </c>
       <c r="F155" s="7">
-        <v>241555</v>
+        <v>87312043</v>
       </c>
       <c r="G155" t="s">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="H155" t="s">
         <v>96</v>
       </c>
       <c r="I155" s="5"/>
       <c r="J155" s="5">
-        <v>0.7315</v>
+        <v>0.7886</v>
       </c>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.25">
@@ -10106,7 +10266,7 @@
         <v>8</v>
       </c>
       <c r="B156" t="s">
-        <v>178</v>
+        <v>146</v>
       </c>
       <c r="C156" t="s">
         <v>115</v>
@@ -10115,20 +10275,20 @@
         <v>60000000</v>
       </c>
       <c r="E156" s="1">
-        <v>88954199</v>
+        <v>91521730</v>
       </c>
       <c r="F156" s="7">
-        <v>-817882</v>
+        <v>91521730</v>
       </c>
       <c r="G156" t="s">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="H156" t="s">
         <v>96</v>
       </c>
       <c r="I156" s="5"/>
       <c r="J156" s="5">
-        <v>0.7315</v>
+        <v>0.7886</v>
       </c>
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.25">
@@ -10136,19 +10296,19 @@
         <v>8</v>
       </c>
       <c r="B157" t="s">
+        <v>150</v>
+      </c>
+      <c r="C157" t="s">
         <v>151</v>
-      </c>
-      <c r="C157" t="s">
-        <v>152</v>
       </c>
       <c r="D157" s="1">
         <v>100000000</v>
       </c>
       <c r="E157" s="1">
-        <v>134048105</v>
+        <v>137712830</v>
       </c>
       <c r="F157" s="7">
-        <v>-178481</v>
+        <v>3664725</v>
       </c>
       <c r="G157" t="s">
         <v>44</v>
@@ -10158,7 +10318,7 @@
       </c>
       <c r="I157" s="5"/>
       <c r="J157" s="5">
-        <v>0.4351</v>
+        <v>0.47340000000000004</v>
       </c>
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.25">
@@ -10166,7 +10326,7 @@
         <v>8</v>
       </c>
       <c r="B158" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C158" t="s">
         <v>121</v>
@@ -10175,10 +10335,10 @@
         <v>100000000</v>
       </c>
       <c r="E158" s="1">
-        <v>136597280</v>
+        <v>140266406</v>
       </c>
       <c r="F158" s="7">
-        <v>54421</v>
+        <v>3669126</v>
       </c>
       <c r="G158" t="s">
         <v>44</v>
@@ -10188,7 +10348,7 @@
       </c>
       <c r="I158" s="5"/>
       <c r="J158" s="5">
-        <v>0.4351</v>
+        <v>0.47340000000000004</v>
       </c>
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.25">
@@ -10196,7 +10356,7 @@
         <v>8</v>
       </c>
       <c r="B159" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C159" t="s">
         <v>105</v>
@@ -10205,10 +10365,10 @@
         <v>100000000</v>
       </c>
       <c r="E159" s="1">
-        <v>137179366</v>
+        <v>140669408</v>
       </c>
       <c r="F159" s="7">
-        <v>333074</v>
+        <v>3490042</v>
       </c>
       <c r="G159" t="s">
         <v>44</v>
@@ -10218,7 +10378,7 @@
       </c>
       <c r="I159" s="5"/>
       <c r="J159" s="5">
-        <v>0.4351</v>
+        <v>0.47340000000000004</v>
       </c>
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.25">
@@ -10226,7 +10386,7 @@
         <v>8</v>
       </c>
       <c r="B160" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C160" t="s">
         <v>120</v>
@@ -10235,10 +10395,10 @@
         <v>100000000</v>
       </c>
       <c r="E160" s="1">
-        <v>136973911</v>
+        <v>140472781</v>
       </c>
       <c r="F160" s="7">
-        <v>235488</v>
+        <v>3498870</v>
       </c>
       <c r="G160" t="s">
         <v>44</v>
@@ -10248,7 +10408,7 @@
       </c>
       <c r="I160" s="5"/>
       <c r="J160" s="5">
-        <v>0.4351</v>
+        <v>0.47340000000000004</v>
       </c>
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.25">
@@ -10256,10 +10416,10 @@
         <v>5</v>
       </c>
       <c r="B161" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C161" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="D161" s="1">
         <v>0</v>
@@ -10268,10 +10428,10 @@
         <v>0</v>
       </c>
       <c r="F161" s="7">
-        <v>-1683240295</v>
+        <v>-897752897</v>
       </c>
       <c r="G161" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H161" t="s">
         <v>96</v>
@@ -10284,10 +10444,10 @@
         <v>5</v>
       </c>
       <c r="B162" t="s">
+        <v>178</v>
+      </c>
+      <c r="C162" t="s">
         <v>179</v>
-      </c>
-      <c r="C162" t="s">
-        <v>79</v>
       </c>
       <c r="D162" s="1">
         <v>0</v>
@@ -10296,10 +10456,10 @@
         <v>0</v>
       </c>
       <c r="F162" s="7">
-        <v>-1687228552</v>
+        <v>-1334569313</v>
       </c>
       <c r="G162" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H162" t="s">
         <v>96</v>
@@ -10312,10 +10472,10 @@
         <v>5</v>
       </c>
       <c r="B163" t="s">
-        <v>119</v>
+        <v>180</v>
       </c>
       <c r="C163" t="s">
-        <v>147</v>
+        <v>103</v>
       </c>
       <c r="D163" s="1">
         <v>0</v>
@@ -10324,10 +10484,10 @@
         <v>0</v>
       </c>
       <c r="F163" s="7">
-        <v>-3924793719</v>
+        <v>-1304933202</v>
       </c>
       <c r="G163" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H163" t="s">
         <v>96</v>
@@ -10340,10 +10500,10 @@
         <v>5</v>
       </c>
       <c r="B164" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C164" t="s">
-        <v>124</v>
+        <v>105</v>
       </c>
       <c r="D164" s="1">
         <v>0</v>
@@ -10352,10 +10512,10 @@
         <v>0</v>
       </c>
       <c r="F164" s="7">
-        <v>-1314198402</v>
+        <v>-1714089252</v>
       </c>
       <c r="G164" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H164" t="s">
         <v>96</v>
@@ -10368,10 +10528,10 @@
         <v>5</v>
       </c>
       <c r="B165" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C165" t="s">
-        <v>125</v>
+        <v>79</v>
       </c>
       <c r="D165" s="1">
         <v>0</v>
@@ -10380,10 +10540,10 @@
         <v>0</v>
       </c>
       <c r="F165" s="7">
-        <v>-1837050463</v>
+        <v>-1711777799</v>
       </c>
       <c r="G165" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H165" t="s">
         <v>96</v>
@@ -10396,10 +10556,10 @@
         <v>5</v>
       </c>
       <c r="B166" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C166" t="s">
-        <v>170</v>
+        <v>110</v>
       </c>
       <c r="D166" s="1">
         <v>0</v>
@@ -10408,10 +10568,10 @@
         <v>0</v>
       </c>
       <c r="F166" s="7">
-        <v>-1216881012</v>
+        <v>-769778438</v>
       </c>
       <c r="G166" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H166" t="s">
         <v>96</v>
@@ -10424,10 +10584,10 @@
         <v>5</v>
       </c>
       <c r="B167" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C167" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D167" s="1">
         <v>0</v>
@@ -10436,10 +10596,10 @@
         <v>0</v>
       </c>
       <c r="F167" s="7">
-        <v>-2051054273</v>
+        <v>-1666508211</v>
       </c>
       <c r="G167" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H167" t="s">
         <v>96</v>
@@ -10452,10 +10612,10 @@
         <v>5</v>
       </c>
       <c r="B168" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C168" t="s">
-        <v>128</v>
+        <v>79</v>
       </c>
       <c r="D168" s="1">
         <v>0</v>
@@ -10464,10 +10624,10 @@
         <v>0</v>
       </c>
       <c r="F168" s="7">
-        <v>-1508632702</v>
+        <v>-1781352129</v>
       </c>
       <c r="G168" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H168" t="s">
         <v>96</v>
@@ -10480,10 +10640,10 @@
         <v>5</v>
       </c>
       <c r="B169" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C169" t="s">
-        <v>182</v>
+        <v>117</v>
       </c>
       <c r="D169" s="1">
         <v>0</v>
@@ -10492,10 +10652,10 @@
         <v>0</v>
       </c>
       <c r="F169" s="7">
-        <v>-422609458</v>
+        <v>-1352096519</v>
       </c>
       <c r="G169" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H169" t="s">
         <v>96</v>
@@ -10508,10 +10668,10 @@
         <v>5</v>
       </c>
       <c r="B170" t="s">
-        <v>151</v>
+        <v>184</v>
       </c>
       <c r="C170" t="s">
-        <v>147</v>
+        <v>79</v>
       </c>
       <c r="D170" s="1">
         <v>0</v>
@@ -10520,10 +10680,10 @@
         <v>0</v>
       </c>
       <c r="F170" s="7">
-        <v>-543970609</v>
+        <v>-760653316</v>
       </c>
       <c r="G170" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H170" t="s">
         <v>96</v>
@@ -10533,13 +10693,13 @@
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B171" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C171" t="s">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="D171" s="1">
         <v>0</v>
@@ -10548,10 +10708,10 @@
         <v>0</v>
       </c>
       <c r="F171" s="7">
-        <v>-303753501</v>
+        <v>-1065528056</v>
       </c>
       <c r="G171" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H171" t="s">
         <v>96</v>
@@ -10561,13 +10721,13 @@
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B172" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C172" t="s">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="D172" s="1">
         <v>0</v>
@@ -10576,10 +10736,10 @@
         <v>0</v>
       </c>
       <c r="F172" s="7">
-        <v>-456179013</v>
+        <v>-1656860388</v>
       </c>
       <c r="G172" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H172" t="s">
         <v>96</v>
@@ -10589,13 +10749,13 @@
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B173" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
       <c r="C173" t="s">
-        <v>157</v>
+        <v>186</v>
       </c>
       <c r="D173" s="1">
         <v>0</v>
@@ -10604,10 +10764,10 @@
         <v>0</v>
       </c>
       <c r="F173" s="7">
-        <v>-361201485</v>
+        <v>-593041556</v>
       </c>
       <c r="G173" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H173" t="s">
         <v>96</v>
@@ -10620,10 +10780,10 @@
         <v>6</v>
       </c>
       <c r="B174" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C174" t="s">
-        <v>135</v>
+        <v>79</v>
       </c>
       <c r="D174" s="1">
         <v>0</v>
@@ -10632,10 +10792,10 @@
         <v>0</v>
       </c>
       <c r="F174" s="7">
-        <v>-405779245</v>
+        <v>-308345333</v>
       </c>
       <c r="G174" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H174" t="s">
         <v>96</v>
@@ -10648,10 +10808,10 @@
         <v>6</v>
       </c>
       <c r="B175" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="C175" t="s">
-        <v>170</v>
+        <v>105</v>
       </c>
       <c r="D175" s="1">
         <v>0</v>
@@ -10660,10 +10820,10 @@
         <v>0</v>
       </c>
       <c r="F175" s="7">
-        <v>-282822171</v>
+        <v>-464380516</v>
       </c>
       <c r="G175" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H175" t="s">
         <v>96</v>
@@ -10676,10 +10836,10 @@
         <v>6</v>
       </c>
       <c r="B176" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="C176" t="s">
-        <v>101</v>
+        <v>156</v>
       </c>
       <c r="D176" s="1">
         <v>0</v>
@@ -10688,10 +10848,10 @@
         <v>0</v>
       </c>
       <c r="F176" s="7">
-        <v>-746373228</v>
+        <v>-367521178</v>
       </c>
       <c r="G176" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H176" t="s">
         <v>96</v>
@@ -10704,10 +10864,10 @@
         <v>6</v>
       </c>
       <c r="B177" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="C177" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="D177" s="1">
         <v>0</v>
@@ -10716,10 +10876,10 @@
         <v>0</v>
       </c>
       <c r="F177" s="7">
-        <v>-442398214</v>
+        <v>-412290581</v>
       </c>
       <c r="G177" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H177" t="s">
         <v>96</v>
@@ -10732,10 +10892,10 @@
         <v>6</v>
       </c>
       <c r="B178" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="C178" t="s">
-        <v>182</v>
+        <v>79</v>
       </c>
       <c r="D178" s="1">
         <v>0</v>
@@ -10744,10 +10904,10 @@
         <v>0</v>
       </c>
       <c r="F178" s="7">
-        <v>-216266708</v>
+        <v>-1013212614</v>
       </c>
       <c r="G178" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H178" t="s">
         <v>96</v>
@@ -10760,10 +10920,10 @@
         <v>7</v>
       </c>
       <c r="B179" t="s">
-        <v>68</v>
+        <v>189</v>
       </c>
       <c r="C179" t="s">
-        <v>170</v>
+        <v>114</v>
       </c>
       <c r="D179" s="1">
         <v>0</v>
@@ -10772,13 +10932,13 @@
         <v>0</v>
       </c>
       <c r="F179" s="7">
-        <v>-1353674960</v>
+        <v>-1255172172</v>
       </c>
       <c r="G179" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H179" t="s">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="I179" s="5"/>
       <c r="J179" s="5"/>
@@ -10788,10 +10948,10 @@
         <v>7</v>
       </c>
       <c r="B180" t="s">
-        <v>68</v>
+        <v>190</v>
       </c>
       <c r="C180" t="s">
-        <v>48</v>
+        <v>179</v>
       </c>
       <c r="D180" s="1">
         <v>0</v>
@@ -10800,13 +10960,13 @@
         <v>0</v>
       </c>
       <c r="F180" s="7">
-        <v>-1334664633</v>
+        <v>-374599171</v>
       </c>
       <c r="G180" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H180" t="s">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="I180" s="5"/>
       <c r="J180" s="5"/>
@@ -10816,10 +10976,10 @@
         <v>7</v>
       </c>
       <c r="B181" t="s">
-        <v>68</v>
+        <v>191</v>
       </c>
       <c r="C181" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="D181" s="1">
         <v>0</v>
@@ -10828,13 +10988,13 @@
         <v>0</v>
       </c>
       <c r="F181" s="7">
-        <v>-1357369868</v>
+        <v>-337505230</v>
       </c>
       <c r="G181" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H181" t="s">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="I181" s="5"/>
       <c r="J181" s="5"/>
@@ -10844,10 +11004,10 @@
         <v>7</v>
       </c>
       <c r="B182" t="s">
-        <v>68</v>
+        <v>191</v>
       </c>
       <c r="C182" t="s">
-        <v>50</v>
+        <v>99</v>
       </c>
       <c r="D182" s="1">
         <v>0</v>
@@ -10856,13 +11016,13 @@
         <v>0</v>
       </c>
       <c r="F182" s="7">
-        <v>-1391420851</v>
+        <v>-1214682638</v>
       </c>
       <c r="G182" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H182" t="s">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="I182" s="5"/>
       <c r="J182" s="5"/>
@@ -10872,10 +11032,10 @@
         <v>7</v>
       </c>
       <c r="B183" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="C183" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="D183" s="1">
         <v>0</v>
@@ -10884,10 +11044,10 @@
         <v>0</v>
       </c>
       <c r="F183" s="7">
-        <v>-534717371</v>
+        <v>-266710574</v>
       </c>
       <c r="G183" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H183" t="s">
         <v>96</v>
@@ -10897,13 +11057,13 @@
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B184" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C184" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D184" s="1">
         <v>0</v>
@@ -10912,10 +11072,10 @@
         <v>0</v>
       </c>
       <c r="F184" s="7">
-        <v>-461631869</v>
+        <v>-334549088</v>
       </c>
       <c r="G184" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H184" t="s">
         <v>96</v>
@@ -10928,10 +11088,10 @@
         <v>8</v>
       </c>
       <c r="B185" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C185" t="s">
-        <v>118</v>
+        <v>79</v>
       </c>
       <c r="D185" s="1">
         <v>0</v>
@@ -10940,10 +11100,10 @@
         <v>0</v>
       </c>
       <c r="F185" s="7">
-        <v>-333967279</v>
+        <v>-265114862</v>
       </c>
       <c r="G185" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H185" t="s">
         <v>96</v>
@@ -10956,10 +11116,10 @@
         <v>8</v>
       </c>
       <c r="B186" t="s">
-        <v>142</v>
+        <v>192</v>
       </c>
       <c r="C186" t="s">
-        <v>143</v>
+        <v>59</v>
       </c>
       <c r="D186" s="1">
         <v>0</v>
@@ -10968,16 +11128,128 @@
         <v>0</v>
       </c>
       <c r="F186" s="7">
-        <v>-73420942</v>
+        <v>-89122293</v>
       </c>
       <c r="G186" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H186" t="s">
         <v>96</v>
       </c>
       <c r="I186" s="5"/>
       <c r="J186" s="5"/>
+    </row>
+    <row r="187" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>8</v>
+      </c>
+      <c r="B187" t="s">
+        <v>192</v>
+      </c>
+      <c r="C187" t="s">
+        <v>121</v>
+      </c>
+      <c r="D187" s="1">
+        <v>0</v>
+      </c>
+      <c r="E187" s="1">
+        <v>0</v>
+      </c>
+      <c r="F187" s="7">
+        <v>-85570319</v>
+      </c>
+      <c r="G187" t="s">
+        <v>92</v>
+      </c>
+      <c r="H187" t="s">
+        <v>96</v>
+      </c>
+      <c r="I187" s="5"/>
+      <c r="J187" s="5"/>
+    </row>
+    <row r="188" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>8</v>
+      </c>
+      <c r="B188" t="s">
+        <v>192</v>
+      </c>
+      <c r="C188" t="s">
+        <v>147</v>
+      </c>
+      <c r="D188" s="1">
+        <v>0</v>
+      </c>
+      <c r="E188" s="1">
+        <v>0</v>
+      </c>
+      <c r="F188" s="7">
+        <v>-87308547</v>
+      </c>
+      <c r="G188" t="s">
+        <v>92</v>
+      </c>
+      <c r="H188" t="s">
+        <v>96</v>
+      </c>
+      <c r="I188" s="5"/>
+      <c r="J188" s="5"/>
+    </row>
+    <row r="189" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>8</v>
+      </c>
+      <c r="B189" t="s">
+        <v>192</v>
+      </c>
+      <c r="C189" t="s">
+        <v>144</v>
+      </c>
+      <c r="D189" s="1">
+        <v>0</v>
+      </c>
+      <c r="E189" s="1">
+        <v>0</v>
+      </c>
+      <c r="F189" s="7">
+        <v>-84636837</v>
+      </c>
+      <c r="G189" t="s">
+        <v>92</v>
+      </c>
+      <c r="H189" t="s">
+        <v>96</v>
+      </c>
+      <c r="I189" s="5"/>
+      <c r="J189" s="5"/>
+    </row>
+    <row r="190" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>8</v>
+      </c>
+      <c r="B190" t="s">
+        <v>192</v>
+      </c>
+      <c r="C190" t="s">
+        <v>115</v>
+      </c>
+      <c r="D190" s="1">
+        <v>0</v>
+      </c>
+      <c r="E190" s="1">
+        <v>0</v>
+      </c>
+      <c r="F190" s="7">
+        <v>-88954199</v>
+      </c>
+      <c r="G190" t="s">
+        <v>92</v>
+      </c>
+      <c r="H190" t="s">
+        <v>96</v>
+      </c>
+      <c r="I190" s="5"/>
+      <c r="J190" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
